--- a/data/nzd0018/nzd0018.xlsx
+++ b/data/nzd0018/nzd0018.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA231"/>
+  <dimension ref="A1:AA232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20517,6 +20517,93 @@
         <v>382.51</v>
       </c>
       <c r="AA231" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>371</v>
+      </c>
+      <c r="C232" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="D232" t="n">
+        <v>358.84</v>
+      </c>
+      <c r="E232" t="n">
+        <v>355.55</v>
+      </c>
+      <c r="F232" t="n">
+        <v>354.49</v>
+      </c>
+      <c r="G232" t="n">
+        <v>347.71</v>
+      </c>
+      <c r="H232" t="n">
+        <v>341.55</v>
+      </c>
+      <c r="I232" t="n">
+        <v>347.25</v>
+      </c>
+      <c r="J232" t="n">
+        <v>353.16</v>
+      </c>
+      <c r="K232" t="n">
+        <v>350.78</v>
+      </c>
+      <c r="L232" t="n">
+        <v>356.95</v>
+      </c>
+      <c r="M232" t="n">
+        <v>373.78</v>
+      </c>
+      <c r="N232" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="O232" t="n">
+        <v>365.51</v>
+      </c>
+      <c r="P232" t="n">
+        <v>368.1</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>376.65</v>
+      </c>
+      <c r="R232" t="n">
+        <v>371.61</v>
+      </c>
+      <c r="S232" t="n">
+        <v>372.18</v>
+      </c>
+      <c r="T232" t="n">
+        <v>375.87</v>
+      </c>
+      <c r="U232" t="n">
+        <v>380.37</v>
+      </c>
+      <c r="V232" t="n">
+        <v>370.99</v>
+      </c>
+      <c r="W232" t="n">
+        <v>363.39</v>
+      </c>
+      <c r="X232" t="n">
+        <v>366.11</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>376.85</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>384.16</v>
+      </c>
+      <c r="AA232" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20533,7 +20620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B234"/>
+  <dimension ref="A1:B235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22876,6 +22963,16 @@
       </c>
       <c r="B234" t="n">
         <v>-0.18</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>
@@ -23044,28 +23141,28 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08232025747297793</v>
+        <v>0.07118367340907632</v>
       </c>
       <c r="J2" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K2" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006338824686740963</v>
+        <v>0.004739915407259709</v>
       </c>
       <c r="M2" t="n">
-        <v>6.396536906629831</v>
+        <v>6.417127821734685</v>
       </c>
       <c r="N2" t="n">
-        <v>61.10361401829171</v>
+        <v>61.54996689172924</v>
       </c>
       <c r="O2" t="n">
-        <v>7.8168800693302</v>
+        <v>7.845378696514862</v>
       </c>
       <c r="P2" t="n">
-        <v>381.7417776492777</v>
+        <v>381.8499580953294</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23122,28 +23219,28 @@
         <v>0.1142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08745929806889723</v>
+        <v>0.07754308024998513</v>
       </c>
       <c r="J3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006415907998242099</v>
+        <v>0.005059330211537039</v>
       </c>
       <c r="M3" t="n">
-        <v>6.894328110036705</v>
+        <v>6.912586320636814</v>
       </c>
       <c r="N3" t="n">
-        <v>68.13689731118038</v>
+        <v>68.40554242700216</v>
       </c>
       <c r="O3" t="n">
-        <v>8.254507696475931</v>
+        <v>8.270764319396495</v>
       </c>
       <c r="P3" t="n">
-        <v>375.2941182974169</v>
+        <v>375.3904441420962</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23200,28 +23297,28 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06380006164662649</v>
+        <v>-0.07462935550103002</v>
       </c>
       <c r="J4" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K4" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002329229307249214</v>
+        <v>0.003194919719362588</v>
       </c>
       <c r="M4" t="n">
-        <v>8.569316565047094</v>
+        <v>8.580649464135224</v>
       </c>
       <c r="N4" t="n">
-        <v>100.286177082659</v>
+        <v>100.5242197926484</v>
       </c>
       <c r="O4" t="n">
-        <v>10.01429863158968</v>
+        <v>10.02617672857647</v>
       </c>
       <c r="P4" t="n">
-        <v>373.067971271539</v>
+        <v>373.173166709644</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23278,28 +23375,28 @@
         <v>0.1014</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1942874521247999</v>
+        <v>-0.2026000079516738</v>
       </c>
       <c r="J5" t="n">
+        <v>231</v>
+      </c>
+      <c r="K5" t="n">
         <v>230</v>
       </c>
-      <c r="K5" t="n">
-        <v>229</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01436358129312754</v>
+        <v>0.01571410258003814</v>
       </c>
       <c r="M5" t="n">
-        <v>10.37365600986305</v>
+        <v>10.36499686617743</v>
       </c>
       <c r="N5" t="n">
-        <v>147.1955767172835</v>
+        <v>146.9447874962673</v>
       </c>
       <c r="O5" t="n">
-        <v>12.13241841997231</v>
+        <v>12.12207851386334</v>
       </c>
       <c r="P5" t="n">
-        <v>370.1770808903263</v>
+        <v>370.2586328926267</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23356,28 +23453,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1893885155929536</v>
+        <v>-0.2006355684012219</v>
       </c>
       <c r="J6" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K6" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008388651537308722</v>
+        <v>0.009471601853077716</v>
       </c>
       <c r="M6" t="n">
-        <v>13.08306166555404</v>
+        <v>13.07609661038611</v>
       </c>
       <c r="N6" t="n">
-        <v>240.7048974263944</v>
+        <v>240.3608680561366</v>
       </c>
       <c r="O6" t="n">
-        <v>15.51466717098354</v>
+        <v>15.50357597640417</v>
       </c>
       <c r="P6" t="n">
-        <v>372.2963033200123</v>
+        <v>372.4070528968681</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23434,28 +23531,28 @@
         <v>0.0711</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2990906061741531</v>
+        <v>-0.308710355395486</v>
       </c>
       <c r="J7" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K7" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02206774741993545</v>
+        <v>0.02365489283147093</v>
       </c>
       <c r="M7" t="n">
-        <v>12.8230592869051</v>
+        <v>12.81117831291287</v>
       </c>
       <c r="N7" t="n">
-        <v>226.2245926522534</v>
+        <v>225.7606191771908</v>
       </c>
       <c r="O7" t="n">
-        <v>15.0407643639628</v>
+        <v>15.0253325812506</v>
       </c>
       <c r="P7" t="n">
-        <v>366.597347899745</v>
+        <v>366.691558015793</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23512,28 +23609,28 @@
         <v>0.0594</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06830123793558895</v>
+        <v>-0.08401167536146174</v>
       </c>
       <c r="J8" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K8" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0008632358876666801</v>
+        <v>0.001312692932181947</v>
       </c>
       <c r="M8" t="n">
-        <v>14.99736371599415</v>
+        <v>15.01378642622041</v>
       </c>
       <c r="N8" t="n">
-        <v>308.1315060822765</v>
+        <v>308.1832969764659</v>
       </c>
       <c r="O8" t="n">
-        <v>17.55367500218335</v>
+        <v>17.55515015533806</v>
       </c>
       <c r="P8" t="n">
-        <v>361.3584947625939</v>
+        <v>361.5123534650405</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23590,28 +23687,28 @@
         <v>0.0771</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3202141387035167</v>
+        <v>-0.3317075490921472</v>
       </c>
       <c r="J9" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K9" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02469829711493765</v>
+        <v>0.02663212288523775</v>
       </c>
       <c r="M9" t="n">
-        <v>13.02879190074261</v>
+        <v>13.03001728605199</v>
       </c>
       <c r="N9" t="n">
-        <v>231.0662324885766</v>
+        <v>230.8050766863486</v>
       </c>
       <c r="O9" t="n">
-        <v>15.20086288631592</v>
+        <v>15.19227029401296</v>
       </c>
       <c r="P9" t="n">
-        <v>368.8392986743082</v>
+        <v>368.9518583161021</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23668,28 +23765,28 @@
         <v>0.1197</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.02189124597975829</v>
+        <v>-0.03382389341916183</v>
       </c>
       <c r="J10" t="n">
+        <v>231</v>
+      </c>
+      <c r="K10" t="n">
         <v>230</v>
       </c>
-      <c r="K10" t="n">
-        <v>229</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0001399374890466154</v>
+        <v>0.0003360049850235081</v>
       </c>
       <c r="M10" t="n">
-        <v>11.65951330549583</v>
+        <v>11.66490903889018</v>
       </c>
       <c r="N10" t="n">
-        <v>194.5796217077247</v>
+        <v>194.535611348272</v>
       </c>
       <c r="O10" t="n">
-        <v>13.94917996542179</v>
+        <v>13.94760235123844</v>
       </c>
       <c r="P10" t="n">
-        <v>367.41323831303</v>
+        <v>367.5303059528385</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23746,28 +23843,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08712088108382395</v>
+        <v>-0.09968584470817733</v>
       </c>
       <c r="J11" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K11" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002138104625876158</v>
+        <v>0.002813190062486259</v>
       </c>
       <c r="M11" t="n">
-        <v>11.86289685290247</v>
+        <v>11.86815371543407</v>
       </c>
       <c r="N11" t="n">
-        <v>201.6158696023549</v>
+        <v>201.6250931301734</v>
       </c>
       <c r="O11" t="n">
-        <v>14.19915031268966</v>
+        <v>14.19947510051598</v>
       </c>
       <c r="P11" t="n">
-        <v>367.442825755393</v>
+        <v>367.5664265006625</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23824,28 +23921,28 @@
         <v>0.0809</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3791649552434039</v>
+        <v>-0.3891967633849195</v>
       </c>
       <c r="J12" t="n">
+        <v>231</v>
+      </c>
+      <c r="K12" t="n">
         <v>230</v>
       </c>
-      <c r="K12" t="n">
-        <v>229</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.03450252019073641</v>
+        <v>0.03655227737807432</v>
       </c>
       <c r="M12" t="n">
-        <v>12.56358777648186</v>
+        <v>12.55731438673862</v>
       </c>
       <c r="N12" t="n">
-        <v>228.6167016168651</v>
+        <v>228.1895457711836</v>
       </c>
       <c r="O12" t="n">
-        <v>15.12007611147726</v>
+        <v>15.10594405428484</v>
       </c>
       <c r="P12" t="n">
-        <v>378.4115798769871</v>
+        <v>378.5099989502149</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23902,28 +23999,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06010525167388091</v>
+        <v>-0.06873627603058614</v>
       </c>
       <c r="J13" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K13" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001163826979325266</v>
+        <v>0.001533180233768694</v>
       </c>
       <c r="M13" t="n">
-        <v>11.34530877134489</v>
+        <v>11.33364226456201</v>
       </c>
       <c r="N13" t="n">
-        <v>178.3423800721208</v>
+        <v>177.9973188295597</v>
       </c>
       <c r="O13" t="n">
-        <v>13.35448913557238</v>
+        <v>13.34156358263752</v>
       </c>
       <c r="P13" t="n">
-        <v>385.3615461314325</v>
+        <v>385.4453876450811</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -23980,28 +24077,28 @@
         <v>0.079</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.02861179654055756</v>
+        <v>-0.04202795492767455</v>
       </c>
       <c r="J14" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K14" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0002763546652073678</v>
+        <v>0.0005984676889927432</v>
       </c>
       <c r="M14" t="n">
-        <v>10.80356257402418</v>
+        <v>10.81506326006714</v>
       </c>
       <c r="N14" t="n">
-        <v>170.3441787300052</v>
+        <v>170.6384331651319</v>
       </c>
       <c r="O14" t="n">
-        <v>13.05159678851615</v>
+        <v>13.06286466151785</v>
       </c>
       <c r="P14" t="n">
-        <v>384.5060206609101</v>
+        <v>384.6363448240729</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24058,28 +24155,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08343932257450022</v>
+        <v>0.06600032150526618</v>
       </c>
       <c r="J15" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K15" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002414197944543783</v>
+        <v>0.001511148539201534</v>
       </c>
       <c r="M15" t="n">
-        <v>10.75493887658129</v>
+        <v>10.78282172935339</v>
       </c>
       <c r="N15" t="n">
-        <v>165.478966376464</v>
+        <v>166.5057373584894</v>
       </c>
       <c r="O15" t="n">
-        <v>12.86386280929892</v>
+        <v>12.90371021677445</v>
       </c>
       <c r="P15" t="n">
-        <v>383.5271747826275</v>
+        <v>383.6965767198411</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24136,28 +24233,28 @@
         <v>0.0737</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.001567670548416468</v>
+        <v>-0.01890922553140926</v>
       </c>
       <c r="J16" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K16" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L16" t="n">
-        <v>9.162000413898141e-07</v>
+        <v>0.0001331331768021915</v>
       </c>
       <c r="M16" t="n">
-        <v>10.25269913661383</v>
+        <v>10.28415313649555</v>
       </c>
       <c r="N16" t="n">
-        <v>154.2917733329291</v>
+        <v>155.3475475367857</v>
       </c>
       <c r="O16" t="n">
-        <v>12.42142396558982</v>
+        <v>12.46384962749414</v>
       </c>
       <c r="P16" t="n">
-        <v>388.2409316062214</v>
+        <v>388.4093869550543</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24214,28 +24311,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2256586059562743</v>
+        <v>-0.2349444764626255</v>
       </c>
       <c r="J17" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K17" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0184147102534068</v>
+        <v>0.02006519882765834</v>
       </c>
       <c r="M17" t="n">
-        <v>10.13506168773799</v>
+        <v>10.13418077225256</v>
       </c>
       <c r="N17" t="n">
-        <v>156.1316071394206</v>
+        <v>155.9499458622043</v>
       </c>
       <c r="O17" t="n">
-        <v>12.49526338815715</v>
+        <v>12.48799206686985</v>
       </c>
       <c r="P17" t="n">
-        <v>393.3381664390073</v>
+        <v>393.4283691086583</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24292,28 +24389,28 @@
         <v>0.0731</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1144871684147187</v>
+        <v>-0.1268214030980406</v>
       </c>
       <c r="J18" t="n">
+        <v>231</v>
+      </c>
+      <c r="K18" t="n">
         <v>230</v>
       </c>
-      <c r="K18" t="n">
-        <v>229</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.004218392049989528</v>
+        <v>0.005197830432515649</v>
       </c>
       <c r="M18" t="n">
-        <v>10.86685787728617</v>
+        <v>10.8748008618755</v>
       </c>
       <c r="N18" t="n">
-        <v>177.3220607672208</v>
+        <v>177.4196611582079</v>
       </c>
       <c r="O18" t="n">
-        <v>13.31623297960879</v>
+        <v>13.31989719022665</v>
       </c>
       <c r="P18" t="n">
-        <v>388.8541831609558</v>
+        <v>388.9745372243236</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24370,28 +24467,28 @@
         <v>0.0774</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2205182652930643</v>
+        <v>-0.2316226973537596</v>
       </c>
       <c r="J19" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K19" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01660127423481716</v>
+        <v>0.01838778995463608</v>
       </c>
       <c r="M19" t="n">
-        <v>10.50560991935858</v>
+        <v>10.50968269413467</v>
       </c>
       <c r="N19" t="n">
-        <v>165.6918813864702</v>
+        <v>165.6813724681278</v>
       </c>
       <c r="O19" t="n">
-        <v>12.87213585177185</v>
+        <v>12.8717276411571</v>
       </c>
       <c r="P19" t="n">
-        <v>390.8379738385425</v>
+        <v>390.9458419609924</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24448,28 +24545,28 @@
         <v>0.063</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1951993839802019</v>
+        <v>-0.2038903695069989</v>
       </c>
       <c r="J20" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K20" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01182581716786479</v>
+        <v>0.01298639887548247</v>
       </c>
       <c r="M20" t="n">
-        <v>11.08982852980054</v>
+        <v>11.08528746274541</v>
       </c>
       <c r="N20" t="n">
-        <v>183.139955919061</v>
+        <v>182.780079211749</v>
       </c>
       <c r="O20" t="n">
-        <v>13.5329211894203</v>
+        <v>13.51961830865609</v>
       </c>
       <c r="P20" t="n">
-        <v>391.0688090936609</v>
+        <v>391.1532330683307</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24526,28 +24623,28 @@
         <v>0.0594</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2314591600024599</v>
+        <v>-0.2393498741821126</v>
       </c>
       <c r="J21" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K21" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01621691113592161</v>
+        <v>0.01746086334637231</v>
       </c>
       <c r="M21" t="n">
-        <v>11.07612827909542</v>
+        <v>11.06754045910294</v>
       </c>
       <c r="N21" t="n">
-        <v>186.9406886092931</v>
+        <v>186.4882991096831</v>
       </c>
       <c r="O21" t="n">
-        <v>13.67262551996847</v>
+        <v>13.65607187699608</v>
       </c>
       <c r="P21" t="n">
-        <v>395.5921252504706</v>
+        <v>395.668775413099</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24604,28 +24701,28 @@
         <v>0.0436</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.002017973366742137</v>
+        <v>-0.01426429596288738</v>
       </c>
       <c r="J22" t="n">
+        <v>231</v>
+      </c>
+      <c r="K22" t="n">
         <v>230</v>
       </c>
-      <c r="K22" t="n">
-        <v>229</v>
-      </c>
       <c r="L22" t="n">
-        <v>7.806882282856975e-07</v>
+        <v>3.928611849213226e-05</v>
       </c>
       <c r="M22" t="n">
-        <v>13.77456281094988</v>
+        <v>13.78176067624314</v>
       </c>
       <c r="N22" t="n">
-        <v>301.3059893402605</v>
+        <v>300.8599570696371</v>
       </c>
       <c r="O22" t="n">
-        <v>17.35816779905818</v>
+        <v>17.34531513318905</v>
       </c>
       <c r="P22" t="n">
-        <v>385.2415478900569</v>
+        <v>385.3602928205204</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24682,28 +24779,28 @@
         <v>0.0402</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0981018295744699</v>
+        <v>-0.1128691314087952</v>
       </c>
       <c r="J23" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K23" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001668841203971594</v>
+        <v>0.002221714482531501</v>
       </c>
       <c r="M23" t="n">
-        <v>14.91183544535258</v>
+        <v>14.92668616878176</v>
       </c>
       <c r="N23" t="n">
-        <v>330.9088403313601</v>
+        <v>330.7128544374863</v>
       </c>
       <c r="O23" t="n">
-        <v>18.19089993187143</v>
+        <v>18.18551221267871</v>
       </c>
       <c r="P23" t="n">
-        <v>383.0053091887559</v>
+        <v>383.1492764837337</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24760,28 +24857,28 @@
         <v>0.0493</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3258723890026526</v>
+        <v>0.3061646279992459</v>
       </c>
       <c r="J24" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K24" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02287991222917307</v>
+        <v>0.02028077330104461</v>
       </c>
       <c r="M24" t="n">
-        <v>13.02186536033705</v>
+        <v>13.0722696084813</v>
       </c>
       <c r="N24" t="n">
-        <v>259.4061988173221</v>
+        <v>260.4802272606406</v>
       </c>
       <c r="O24" t="n">
-        <v>16.10609197841991</v>
+        <v>16.1393998420214</v>
       </c>
       <c r="P24" t="n">
-        <v>380.1728568806973</v>
+        <v>380.3659979305968</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24838,28 +24935,28 @@
         <v>0.0531</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3900425907941186</v>
+        <v>0.3760558715189027</v>
       </c>
       <c r="J25" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K25" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L25" t="n">
-        <v>0.03601111410712776</v>
+        <v>0.03373084116314762</v>
       </c>
       <c r="M25" t="n">
-        <v>12.38068148040182</v>
+        <v>12.39163884984839</v>
       </c>
       <c r="N25" t="n">
-        <v>232.943806237934</v>
+        <v>233.0361559235007</v>
       </c>
       <c r="O25" t="n">
-        <v>15.26249672360109</v>
+        <v>15.26552180318448</v>
       </c>
       <c r="P25" t="n">
-        <v>382.6548080309189</v>
+        <v>382.7918814227161</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -24916,28 +25013,28 @@
         <v>0.0699</v>
       </c>
       <c r="I26" t="n">
-        <v>0.237350934683148</v>
+        <v>0.2310302765339731</v>
       </c>
       <c r="J26" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K26" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01521462353239855</v>
+        <v>0.01455450882382003</v>
       </c>
       <c r="M26" t="n">
-        <v>11.50265383819208</v>
+        <v>11.48594449114325</v>
       </c>
       <c r="N26" t="n">
-        <v>208.5709917170258</v>
+        <v>207.8837116739468</v>
       </c>
       <c r="O26" t="n">
-        <v>14.44198711109471</v>
+        <v>14.41817296587702</v>
       </c>
       <c r="P26" t="n">
-        <v>385.1811898313687</v>
+        <v>385.2431338822823</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -24975,7 +25072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA231"/>
+  <dimension ref="A1:AA232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56513,6 +56610,143 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>-34.7719051044483,173.14920079029756</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>-34.7724478145552,173.1485913126274</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>-34.77302221156782,173.14802701986477</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-34.77368587217956,173.14762190060316</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-34.774365230873066,173.14723600433524</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-34.77509588175112,173.14702053208035</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-34.775834407685544,173.14682774810836</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-34.77658759869113,173.14689015670893</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-34.77733149549751,173.14699858320566</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-34.77806876529097,173.14712325232637</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-34.778785289142796,173.14735186543714</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>-34.77947555471944,173.1476928592327</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-34.78017038700532,173.14795729234612</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-34.780856164228425,173.14828782738914</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>-34.78152244087913,173.14867118264814</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>-34.782134297126255,173.14916273687018</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>-34.78277581287934,173.14959738349643</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>-34.78339456580924,173.15008668833067</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>-34.78399814788818,173.15060471637167</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>-34.78459206241291,173.1511258738311</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>-34.78521902273425,173.15159023794303</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>-34.78582879545117,173.15210072610583</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>-34.78638761589595,173.15268789249163</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>-34.786909400285026,173.15333360929577</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>-34.787450092166864,173.15394972228796</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0018/nzd0018.xlsx
+++ b/data/nzd0018/nzd0018.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA232"/>
+  <dimension ref="A1:AA233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20604,6 +20604,93 @@
         <v>384.16</v>
       </c>
       <c r="AA232" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>373.21</v>
+      </c>
+      <c r="C233" t="n">
+        <v>367.64</v>
+      </c>
+      <c r="D233" t="n">
+        <v>361.21</v>
+      </c>
+      <c r="E233" t="n">
+        <v>357.09</v>
+      </c>
+      <c r="F233" t="n">
+        <v>354.98</v>
+      </c>
+      <c r="G233" t="n">
+        <v>349.71</v>
+      </c>
+      <c r="H233" t="n">
+        <v>343.11</v>
+      </c>
+      <c r="I233" t="n">
+        <v>348.59</v>
+      </c>
+      <c r="J233" t="n">
+        <v>355.21</v>
+      </c>
+      <c r="K233" t="n">
+        <v>353.96</v>
+      </c>
+      <c r="L233" t="n">
+        <v>359.06</v>
+      </c>
+      <c r="M233" t="n">
+        <v>375.89</v>
+      </c>
+      <c r="N233" t="n">
+        <v>371.03</v>
+      </c>
+      <c r="O233" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="P233" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>378.26</v>
+      </c>
+      <c r="R233" t="n">
+        <v>373.08</v>
+      </c>
+      <c r="S233" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="T233" t="n">
+        <v>376.87</v>
+      </c>
+      <c r="U233" t="n">
+        <v>382.11</v>
+      </c>
+      <c r="V233" t="n">
+        <v>373.46</v>
+      </c>
+      <c r="W233" t="n">
+        <v>365.88</v>
+      </c>
+      <c r="X233" t="n">
+        <v>368.08</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>379.24</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>386.45</v>
+      </c>
+      <c r="AA233" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20620,7 +20707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B235"/>
+  <dimension ref="A1:B236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22973,6 +23060,16 @@
       </c>
       <c r="B235" t="n">
         <v>0.45</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -23141,28 +23238,28 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07118367340907632</v>
+        <v>0.06220630571677082</v>
       </c>
       <c r="J2" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K2" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004739915407259709</v>
+        <v>0.003632110214795814</v>
       </c>
       <c r="M2" t="n">
-        <v>6.417127821734685</v>
+        <v>6.429404471431133</v>
       </c>
       <c r="N2" t="n">
-        <v>61.54996689172924</v>
+        <v>61.75439687165974</v>
       </c>
       <c r="O2" t="n">
-        <v>7.845378696514862</v>
+        <v>7.858396584015071</v>
       </c>
       <c r="P2" t="n">
-        <v>381.8499580953294</v>
+        <v>381.9373344490119</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23219,28 +23316,28 @@
         <v>0.1142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07754308024998513</v>
+        <v>0.06917995291246831</v>
       </c>
       <c r="J3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005059330211537039</v>
+        <v>0.004046978416069713</v>
       </c>
       <c r="M3" t="n">
-        <v>6.912586320636814</v>
+        <v>6.923037676716821</v>
       </c>
       <c r="N3" t="n">
-        <v>68.40554242700216</v>
+        <v>68.51834253471706</v>
       </c>
       <c r="O3" t="n">
-        <v>8.270764319396495</v>
+        <v>8.277580717499351</v>
       </c>
       <c r="P3" t="n">
-        <v>375.3904441420962</v>
+        <v>375.4718421194521</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23297,28 +23394,28 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07462935550103002</v>
+        <v>-0.08316917020610003</v>
       </c>
       <c r="J4" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K4" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003194919719362588</v>
+        <v>0.003987427388298492</v>
       </c>
       <c r="M4" t="n">
-        <v>8.580649464135224</v>
+        <v>8.582589026932999</v>
       </c>
       <c r="N4" t="n">
-        <v>100.5242197926484</v>
+        <v>100.5159841486868</v>
       </c>
       <c r="O4" t="n">
-        <v>10.02617672857647</v>
+        <v>10.02576601306288</v>
       </c>
       <c r="P4" t="n">
-        <v>373.173166709644</v>
+        <v>373.2562843779436</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23375,28 +23472,28 @@
         <v>0.1014</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2026000079516738</v>
+        <v>-0.2093700961146957</v>
       </c>
       <c r="J5" t="n">
+        <v>232</v>
+      </c>
+      <c r="K5" t="n">
         <v>231</v>
       </c>
-      <c r="K5" t="n">
-        <v>230</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01571410258003814</v>
+        <v>0.01689951657585076</v>
       </c>
       <c r="M5" t="n">
-        <v>10.36499686617743</v>
+        <v>10.35002752547147</v>
       </c>
       <c r="N5" t="n">
-        <v>146.9447874962673</v>
+        <v>146.5711960388595</v>
       </c>
       <c r="O5" t="n">
-        <v>12.12207851386334</v>
+        <v>12.10665916092707</v>
       </c>
       <c r="P5" t="n">
-        <v>370.2586328926267</v>
+        <v>370.3251806358355</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23453,28 +23550,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2006355684012219</v>
+        <v>-0.2111734943199164</v>
       </c>
       <c r="J6" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K6" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009471601853077716</v>
+        <v>0.01055831485406189</v>
       </c>
       <c r="M6" t="n">
-        <v>13.07609661038611</v>
+        <v>13.06583904817546</v>
       </c>
       <c r="N6" t="n">
-        <v>240.3608680561366</v>
+        <v>239.9466299001406</v>
       </c>
       <c r="O6" t="n">
-        <v>15.50357597640417</v>
+        <v>15.49021077649173</v>
       </c>
       <c r="P6" t="n">
-        <v>372.4070528968681</v>
+        <v>372.5110213576787</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23531,28 +23628,28 @@
         <v>0.0711</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.308710355395486</v>
+        <v>-0.3163518116574651</v>
       </c>
       <c r="J7" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K7" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02365489283147093</v>
+        <v>0.02501703920497333</v>
       </c>
       <c r="M7" t="n">
-        <v>12.81117831291287</v>
+        <v>12.7902234362669</v>
       </c>
       <c r="N7" t="n">
-        <v>225.7606191771908</v>
+        <v>225.115236153609</v>
       </c>
       <c r="O7" t="n">
-        <v>15.0253325812506</v>
+        <v>15.00384071341765</v>
       </c>
       <c r="P7" t="n">
-        <v>366.691558015793</v>
+        <v>366.7665396373706</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23609,28 +23706,28 @@
         <v>0.0594</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08401167536146174</v>
+        <v>-0.09798127379465352</v>
       </c>
       <c r="J8" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K8" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001312692932181947</v>
+        <v>0.001795992499544985</v>
       </c>
       <c r="M8" t="n">
-        <v>15.01378642622041</v>
+        <v>15.02075809979803</v>
       </c>
       <c r="N8" t="n">
-        <v>308.1832969764659</v>
+        <v>307.9669231208753</v>
       </c>
       <c r="O8" t="n">
-        <v>17.55515015533806</v>
+        <v>17.54898638442902</v>
       </c>
       <c r="P8" t="n">
-        <v>361.5123534650405</v>
+        <v>361.6494298425526</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23687,28 +23784,28 @@
         <v>0.0771</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3317075490921472</v>
+        <v>-0.3417448167234349</v>
       </c>
       <c r="J9" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K9" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02663212288523775</v>
+        <v>0.02842722787566954</v>
       </c>
       <c r="M9" t="n">
-        <v>13.03001728605199</v>
+        <v>13.02392817040471</v>
       </c>
       <c r="N9" t="n">
-        <v>230.8050766863486</v>
+        <v>230.3816149985416</v>
       </c>
       <c r="O9" t="n">
-        <v>15.19227029401296</v>
+        <v>15.17832714756609</v>
       </c>
       <c r="P9" t="n">
-        <v>368.9518583161021</v>
+        <v>369.0503487840705</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23765,28 +23862,28 @@
         <v>0.1197</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03382389341916183</v>
+        <v>-0.04369264170606683</v>
       </c>
       <c r="J10" t="n">
+        <v>232</v>
+      </c>
+      <c r="K10" t="n">
         <v>231</v>
       </c>
-      <c r="K10" t="n">
-        <v>230</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0003360049850235081</v>
+        <v>0.000564550867730107</v>
       </c>
       <c r="M10" t="n">
-        <v>11.66490903889018</v>
+        <v>11.66043663024471</v>
       </c>
       <c r="N10" t="n">
-        <v>194.535611348272</v>
+        <v>194.251318709299</v>
       </c>
       <c r="O10" t="n">
-        <v>13.94760235123844</v>
+        <v>13.93740717311864</v>
       </c>
       <c r="P10" t="n">
-        <v>367.5303059528385</v>
+        <v>367.6273125074026</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23843,28 +23940,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.09968584470817733</v>
+        <v>-0.1091819473325835</v>
       </c>
       <c r="J11" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K11" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002813190062486259</v>
+        <v>0.003397660443766992</v>
       </c>
       <c r="M11" t="n">
-        <v>11.86815371543407</v>
+        <v>11.85932789039618</v>
       </c>
       <c r="N11" t="n">
-        <v>201.6250931301734</v>
+        <v>201.2635976485302</v>
       </c>
       <c r="O11" t="n">
-        <v>14.19947510051598</v>
+        <v>14.1867402051539</v>
       </c>
       <c r="P11" t="n">
-        <v>367.5664265006625</v>
+        <v>367.6600213737871</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -23921,28 +24018,28 @@
         <v>0.0809</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3891967633849195</v>
+        <v>-0.397151859174689</v>
       </c>
       <c r="J12" t="n">
+        <v>232</v>
+      </c>
+      <c r="K12" t="n">
         <v>231</v>
       </c>
-      <c r="K12" t="n">
-        <v>230</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.03655227737807432</v>
+        <v>0.03831236836231611</v>
       </c>
       <c r="M12" t="n">
-        <v>12.55731438673862</v>
+        <v>12.54099088978127</v>
       </c>
       <c r="N12" t="n">
-        <v>228.1895457711836</v>
+        <v>227.5641941606353</v>
       </c>
       <c r="O12" t="n">
-        <v>15.10594405428484</v>
+        <v>15.08523099460646</v>
       </c>
       <c r="P12" t="n">
-        <v>378.5099989502149</v>
+        <v>378.5881949292142</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -23999,28 +24096,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06873627603058614</v>
+        <v>-0.07535560381132925</v>
       </c>
       <c r="J13" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K13" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001533180233768694</v>
+        <v>0.00185780057376006</v>
       </c>
       <c r="M13" t="n">
-        <v>11.33364226456201</v>
+        <v>11.31326120330403</v>
       </c>
       <c r="N13" t="n">
-        <v>177.9973188295597</v>
+        <v>177.4854646597412</v>
       </c>
       <c r="O13" t="n">
-        <v>13.34156358263752</v>
+        <v>13.32236708170666</v>
       </c>
       <c r="P13" t="n">
-        <v>385.4453876450811</v>
+        <v>385.5098132924573</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24077,28 +24174,28 @@
         <v>0.079</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.04202795492767455</v>
+        <v>-0.05270398336588549</v>
       </c>
       <c r="J14" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K14" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0005984676889927432</v>
+        <v>0.0009464951283728595</v>
       </c>
       <c r="M14" t="n">
-        <v>10.81506326006714</v>
+        <v>10.81512089401274</v>
       </c>
       <c r="N14" t="n">
-        <v>170.6384331651319</v>
+        <v>170.5672332416553</v>
       </c>
       <c r="O14" t="n">
-        <v>13.06286466151785</v>
+        <v>13.06013909733182</v>
       </c>
       <c r="P14" t="n">
-        <v>384.6363448240729</v>
+        <v>384.7402541735296</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24155,28 +24252,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06600032150526618</v>
+        <v>0.05145572446855062</v>
       </c>
       <c r="J15" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K15" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001511148539201534</v>
+        <v>0.0009213704887817142</v>
       </c>
       <c r="M15" t="n">
-        <v>10.78282172935339</v>
+        <v>10.79790036212557</v>
       </c>
       <c r="N15" t="n">
-        <v>166.5057373584894</v>
+        <v>167.0210175741392</v>
       </c>
       <c r="O15" t="n">
-        <v>12.90371021677445</v>
+        <v>12.92366115209383</v>
       </c>
       <c r="P15" t="n">
-        <v>383.6965767198411</v>
+        <v>383.83813868972</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24233,28 +24330,28 @@
         <v>0.0737</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01890922553140926</v>
+        <v>-0.0336314178284776</v>
       </c>
       <c r="J16" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K16" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0001331331768021915</v>
+        <v>0.0004217786351226049</v>
       </c>
       <c r="M16" t="n">
-        <v>10.28415313649555</v>
+        <v>10.30408735428666</v>
       </c>
       <c r="N16" t="n">
-        <v>155.3475475367857</v>
+        <v>155.9412175060993</v>
       </c>
       <c r="O16" t="n">
-        <v>12.46384962749414</v>
+        <v>12.48764259202269</v>
       </c>
       <c r="P16" t="n">
-        <v>388.4093869550543</v>
+        <v>388.5526774523604</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24311,28 +24408,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2349444764626255</v>
+        <v>-0.242620246804943</v>
       </c>
       <c r="J17" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K17" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02006519882765834</v>
+        <v>0.02153132528238255</v>
       </c>
       <c r="M17" t="n">
-        <v>10.13418077225256</v>
+        <v>10.12574656390384</v>
       </c>
       <c r="N17" t="n">
-        <v>155.9499458622043</v>
+        <v>155.6211441576811</v>
       </c>
       <c r="O17" t="n">
-        <v>12.48799206686985</v>
+        <v>12.47482040582874</v>
       </c>
       <c r="P17" t="n">
-        <v>393.4283691086583</v>
+        <v>393.5030770684082</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24389,28 +24486,28 @@
         <v>0.0731</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1268214030980406</v>
+        <v>-0.137584516689429</v>
       </c>
       <c r="J18" t="n">
+        <v>232</v>
+      </c>
+      <c r="K18" t="n">
         <v>231</v>
       </c>
-      <c r="K18" t="n">
-        <v>230</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.005197830432515649</v>
+        <v>0.006149285208632338</v>
       </c>
       <c r="M18" t="n">
-        <v>10.8748008618755</v>
+        <v>10.87547999715244</v>
       </c>
       <c r="N18" t="n">
-        <v>177.4196611582079</v>
+        <v>177.3241486493621</v>
       </c>
       <c r="O18" t="n">
-        <v>13.31989719022665</v>
+        <v>13.31631137550343</v>
       </c>
       <c r="P18" t="n">
-        <v>388.9745372243236</v>
+        <v>389.0797659400448</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24467,28 +24564,28 @@
         <v>0.0774</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2316226973537596</v>
+        <v>-0.2409984339158525</v>
       </c>
       <c r="J19" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K19" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01838778995463608</v>
+        <v>0.02000986283980577</v>
       </c>
       <c r="M19" t="n">
-        <v>10.50968269413467</v>
+        <v>10.50712363640285</v>
       </c>
       <c r="N19" t="n">
-        <v>165.6813724681278</v>
+        <v>165.4795736271326</v>
       </c>
       <c r="O19" t="n">
-        <v>12.8717276411571</v>
+        <v>12.86388641224465</v>
       </c>
       <c r="P19" t="n">
-        <v>390.9458419609924</v>
+        <v>391.0370956226404</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24545,28 +24642,28 @@
         <v>0.063</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2038903695069989</v>
+        <v>-0.2115034428461034</v>
       </c>
       <c r="J20" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K20" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01298639887548247</v>
+        <v>0.01407213993516754</v>
       </c>
       <c r="M20" t="n">
-        <v>11.08528746274541</v>
+        <v>11.0752706834997</v>
       </c>
       <c r="N20" t="n">
-        <v>182.780079211749</v>
+        <v>182.3300434518996</v>
       </c>
       <c r="O20" t="n">
-        <v>13.51961830865609</v>
+        <v>13.50296424685704</v>
       </c>
       <c r="P20" t="n">
-        <v>391.1532330683307</v>
+        <v>391.2273308007047</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24623,28 +24720,28 @@
         <v>0.0594</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2393498741821126</v>
+        <v>-0.2455500440366739</v>
       </c>
       <c r="J21" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K21" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01746086334637231</v>
+        <v>0.01851830720309344</v>
       </c>
       <c r="M21" t="n">
-        <v>11.06754045910294</v>
+        <v>11.05051345725237</v>
       </c>
       <c r="N21" t="n">
-        <v>186.4882991096831</v>
+        <v>185.9085274265076</v>
       </c>
       <c r="O21" t="n">
-        <v>13.65607187699608</v>
+        <v>13.63482773732428</v>
       </c>
       <c r="P21" t="n">
-        <v>395.668775413099</v>
+        <v>395.7291214134714</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24701,28 +24798,28 @@
         <v>0.0436</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.01426429596288738</v>
+        <v>-0.02410228623812671</v>
       </c>
       <c r="J22" t="n">
+        <v>232</v>
+      </c>
+      <c r="K22" t="n">
         <v>231</v>
       </c>
-      <c r="K22" t="n">
-        <v>230</v>
-      </c>
       <c r="L22" t="n">
-        <v>3.928611849213226e-05</v>
+        <v>0.0001130605184064271</v>
       </c>
       <c r="M22" t="n">
-        <v>13.78176067624314</v>
+        <v>13.77556825276728</v>
       </c>
       <c r="N22" t="n">
-        <v>300.8599570696371</v>
+        <v>300.1245233223428</v>
       </c>
       <c r="O22" t="n">
-        <v>17.34531513318905</v>
+        <v>17.32410238143214</v>
       </c>
       <c r="P22" t="n">
-        <v>385.3602928205204</v>
+        <v>385.4558734562505</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24779,28 +24876,28 @@
         <v>0.0402</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1128691314087952</v>
+        <v>-0.1251356237216234</v>
       </c>
       <c r="J23" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K23" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L23" t="n">
-        <v>0.002221714482531501</v>
+        <v>0.002749341167740393</v>
       </c>
       <c r="M23" t="n">
-        <v>14.92668616878176</v>
+        <v>14.93218072233936</v>
       </c>
       <c r="N23" t="n">
-        <v>330.7128544374863</v>
+        <v>330.1513205996131</v>
       </c>
       <c r="O23" t="n">
-        <v>18.18551221267871</v>
+        <v>18.17006660966363</v>
       </c>
       <c r="P23" t="n">
-        <v>383.1492764837337</v>
+        <v>383.2690982230404</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24857,28 +24954,28 @@
         <v>0.0493</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3061646279992459</v>
+        <v>0.2886265244317032</v>
       </c>
       <c r="J24" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K24" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02028077330104461</v>
+        <v>0.01811958100032873</v>
       </c>
       <c r="M24" t="n">
-        <v>13.0722696084813</v>
+        <v>13.11010699191204</v>
       </c>
       <c r="N24" t="n">
-        <v>260.4802272606406</v>
+        <v>261.1239029322113</v>
       </c>
       <c r="O24" t="n">
-        <v>16.1393998420214</v>
+        <v>16.15932866588867</v>
       </c>
       <c r="P24" t="n">
-        <v>380.3659979305968</v>
+        <v>380.538212926735</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -24935,28 +25032,28 @@
         <v>0.0531</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3760558715189027</v>
+        <v>0.3644606801533912</v>
       </c>
       <c r="J25" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K25" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L25" t="n">
-        <v>0.03373084116314762</v>
+        <v>0.03195102906483638</v>
       </c>
       <c r="M25" t="n">
-        <v>12.39163884984839</v>
+        <v>12.39132605704159</v>
       </c>
       <c r="N25" t="n">
-        <v>233.0361559235007</v>
+        <v>232.7970863141456</v>
       </c>
       <c r="O25" t="n">
-        <v>15.26552180318448</v>
+        <v>15.25768941596812</v>
       </c>
       <c r="P25" t="n">
-        <v>382.7918814227161</v>
+        <v>382.9057401320424</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -25013,28 +25110,28 @@
         <v>0.0699</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2310302765339731</v>
+        <v>0.2268334525909768</v>
       </c>
       <c r="J26" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K26" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01455450882382003</v>
+        <v>0.01416923768647826</v>
       </c>
       <c r="M26" t="n">
-        <v>11.48594449114325</v>
+        <v>11.45801564441199</v>
       </c>
       <c r="N26" t="n">
-        <v>207.8837116739468</v>
+        <v>207.0779166874385</v>
       </c>
       <c r="O26" t="n">
-        <v>14.41817296587702</v>
+        <v>14.39020210724778</v>
       </c>
       <c r="P26" t="n">
-        <v>385.2431338822823</v>
+        <v>385.2843444964375</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -25072,7 +25169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA232"/>
+  <dimension ref="A1:AA233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56747,6 +56844,143 @@
         </is>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>-34.77191768559455,173.14921952118362</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>-34.77245606099781,173.1486048540662</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>-34.77303255109348,173.1480496878468</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-34.77369156839568,173.14763724984024</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-34.774366487571996,173.1472411382884</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-34.77509849777215,173.14704215865038</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-34.77583536218147,173.14684475799612</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-34.77658729240954,173.14690479694295</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-34.77732949953158,173.14702085700375</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-34.77806377827272,173.14715747776313</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-34.77878184376548,173.147374545153</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>-34.77947036222363,173.14771504503776</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>-34.7801607042641,173.14798579197773</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>-34.78084577409018,173.14831679513858</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>-34.781512484064336,173.14869654754284</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>-34.78212703523335,173.1491779744595</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>-34.78276866736428,173.14961091637392</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>-34.78338635085714,173.15010224662066</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>-34.783993286944124,173.15061392250715</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>-34.78458300670141,173.15114140521302</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>-34.78520505043755,173.15161126312424</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>-34.785814554168695,173.15212176812827</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>-34.78637656540582,173.1527047523654</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>-34.786896125351845,173.15335418940714</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>-34.78743737260306,173.1539694413702</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0018/nzd0018.xlsx
+++ b/data/nzd0018/nzd0018.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA233"/>
+  <dimension ref="A1:AA235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20691,6 +20691,180 @@
         <v>386.45</v>
       </c>
       <c r="AA233" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>374.35</v>
+      </c>
+      <c r="C234" t="n">
+        <v>368.64</v>
+      </c>
+      <c r="D234" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="E234" t="n">
+        <v>358.62</v>
+      </c>
+      <c r="F234" t="n">
+        <v>358.18</v>
+      </c>
+      <c r="G234" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="H234" t="n">
+        <v>344.65</v>
+      </c>
+      <c r="I234" t="n">
+        <v>348.99</v>
+      </c>
+      <c r="J234" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="K234" t="n">
+        <v>354.88</v>
+      </c>
+      <c r="L234" t="n">
+        <v>358.74</v>
+      </c>
+      <c r="M234" t="n">
+        <v>374.57</v>
+      </c>
+      <c r="N234" t="n">
+        <v>371.99</v>
+      </c>
+      <c r="O234" t="n">
+        <v>368.15</v>
+      </c>
+      <c r="P234" t="n">
+        <v>368.61</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>377.64</v>
+      </c>
+      <c r="R234" t="n">
+        <v>372.51</v>
+      </c>
+      <c r="S234" t="n">
+        <v>372.36</v>
+      </c>
+      <c r="T234" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="U234" t="n">
+        <v>380.25</v>
+      </c>
+      <c r="V234" t="n">
+        <v>371.71</v>
+      </c>
+      <c r="W234" t="n">
+        <v>362.39</v>
+      </c>
+      <c r="X234" t="n">
+        <v>365.61</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>378.39</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>387.79</v>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="C235" t="n">
+        <v>369.73</v>
+      </c>
+      <c r="D235" t="n">
+        <v>364.54</v>
+      </c>
+      <c r="E235" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="F235" t="n">
+        <v>360.65</v>
+      </c>
+      <c r="G235" t="n">
+        <v>354.91</v>
+      </c>
+      <c r="H235" t="n">
+        <v>347.31</v>
+      </c>
+      <c r="I235" t="n">
+        <v>351.57</v>
+      </c>
+      <c r="J235" t="n">
+        <v>356.99</v>
+      </c>
+      <c r="K235" t="n">
+        <v>356.82</v>
+      </c>
+      <c r="L235" t="n">
+        <v>360.72</v>
+      </c>
+      <c r="M235" t="n">
+        <v>375.83</v>
+      </c>
+      <c r="N235" t="n">
+        <v>373.79</v>
+      </c>
+      <c r="O235" t="n">
+        <v>369.67</v>
+      </c>
+      <c r="P235" t="n">
+        <v>370.2</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="R235" t="n">
+        <v>373.65</v>
+      </c>
+      <c r="S235" t="n">
+        <v>373.91</v>
+      </c>
+      <c r="T235" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="U235" t="n">
+        <v>381.38</v>
+      </c>
+      <c r="V235" t="n">
+        <v>373.73</v>
+      </c>
+      <c r="W235" t="n">
+        <v>365.2</v>
+      </c>
+      <c r="X235" t="n">
+        <v>367.59</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>380.07</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>389.54</v>
+      </c>
+      <c r="AA235" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20707,7 +20881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B236"/>
+  <dimension ref="A1:B238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23070,6 +23244,26 @@
       </c>
       <c r="B236" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
@@ -23238,28 +23432,28 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06220630571677082</v>
+        <v>0.04799666502486673</v>
       </c>
       <c r="J2" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K2" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003632110214795814</v>
+        <v>0.002186620199779665</v>
       </c>
       <c r="M2" t="n">
-        <v>6.429404471431133</v>
+        <v>6.439035859646825</v>
       </c>
       <c r="N2" t="n">
-        <v>61.75439687165974</v>
+        <v>61.83178963277663</v>
       </c>
       <c r="O2" t="n">
-        <v>7.858396584015071</v>
+        <v>7.863319250340573</v>
       </c>
       <c r="P2" t="n">
-        <v>381.9373344490119</v>
+        <v>382.0761044319462</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23316,28 +23510,28 @@
         <v>0.1142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06917995291246831</v>
+        <v>0.05562751390699439</v>
       </c>
       <c r="J3" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K3" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004046978416069713</v>
+        <v>0.002650732007624779</v>
       </c>
       <c r="M3" t="n">
-        <v>6.923037676716821</v>
+        <v>6.928115954867519</v>
       </c>
       <c r="N3" t="n">
-        <v>68.51834253471706</v>
+        <v>68.4816913655489</v>
       </c>
       <c r="O3" t="n">
-        <v>8.277580717499351</v>
+        <v>8.275366539649401</v>
       </c>
       <c r="P3" t="n">
-        <v>375.4718421194521</v>
+        <v>375.6041951123505</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23394,28 +23588,28 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08316917020610003</v>
+        <v>-0.09511013078141589</v>
       </c>
       <c r="J4" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K4" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003987427388298492</v>
+        <v>0.005288079050292271</v>
       </c>
       <c r="M4" t="n">
-        <v>8.582589026932999</v>
+        <v>8.562819745449739</v>
       </c>
       <c r="N4" t="n">
-        <v>100.5159841486868</v>
+        <v>100.0844637925589</v>
       </c>
       <c r="O4" t="n">
-        <v>10.02576601306288</v>
+        <v>10.00422229823782</v>
       </c>
       <c r="P4" t="n">
-        <v>373.2562843779436</v>
+        <v>373.3728984906168</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23472,28 +23666,28 @@
         <v>0.1014</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2093700961146957</v>
+        <v>-0.2184293948558713</v>
       </c>
       <c r="J5" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K5" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01689951657585076</v>
+        <v>0.01869338370880058</v>
       </c>
       <c r="M5" t="n">
-        <v>10.35002752547147</v>
+        <v>10.3024960058638</v>
       </c>
       <c r="N5" t="n">
-        <v>146.5711960388595</v>
+        <v>145.5588608008174</v>
       </c>
       <c r="O5" t="n">
-        <v>12.10665916092707</v>
+        <v>12.06477769380014</v>
       </c>
       <c r="P5" t="n">
-        <v>370.3251806358355</v>
+        <v>370.4145257431141</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23550,28 +23744,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2111734943199164</v>
+        <v>-0.2239486929844305</v>
       </c>
       <c r="J6" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K6" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01055831485406189</v>
+        <v>0.01206713572407181</v>
       </c>
       <c r="M6" t="n">
-        <v>13.06583904817546</v>
+        <v>13.00880859023509</v>
       </c>
       <c r="N6" t="n">
-        <v>239.9466299001406</v>
+        <v>238.3592349975545</v>
       </c>
       <c r="O6" t="n">
-        <v>15.49021077649173</v>
+        <v>15.43888710359508</v>
       </c>
       <c r="P6" t="n">
-        <v>372.5110213576787</v>
+        <v>372.6374821516083</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23628,28 +23822,28 @@
         <v>0.0711</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3163518116574651</v>
+        <v>-0.3240573156428198</v>
       </c>
       <c r="J7" t="n">
+        <v>234</v>
+      </c>
+      <c r="K7" t="n">
         <v>232</v>
       </c>
-      <c r="K7" t="n">
-        <v>230</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02501703920497333</v>
+        <v>0.02670349484614665</v>
       </c>
       <c r="M7" t="n">
-        <v>12.7902234362669</v>
+        <v>12.71445284058565</v>
       </c>
       <c r="N7" t="n">
-        <v>225.115236153609</v>
+        <v>223.3587875004459</v>
       </c>
       <c r="O7" t="n">
-        <v>15.00384071341765</v>
+        <v>14.94519278900229</v>
       </c>
       <c r="P7" t="n">
-        <v>366.7665396373706</v>
+        <v>366.842399156261</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23706,28 +23900,28 @@
         <v>0.0594</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09798127379465352</v>
+        <v>-0.1200809783152627</v>
       </c>
       <c r="J8" t="n">
+        <v>234</v>
+      </c>
+      <c r="K8" t="n">
         <v>232</v>
       </c>
-      <c r="K8" t="n">
-        <v>230</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.001795992499544985</v>
+        <v>0.002735509936497627</v>
       </c>
       <c r="M8" t="n">
-        <v>15.02075809979803</v>
+        <v>15.00389930651963</v>
       </c>
       <c r="N8" t="n">
-        <v>307.9669231208753</v>
+        <v>306.7628871261094</v>
       </c>
       <c r="O8" t="n">
-        <v>17.54898638442902</v>
+        <v>17.51464778766931</v>
       </c>
       <c r="P8" t="n">
-        <v>361.6494298425526</v>
+        <v>361.8670121269352</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23784,28 +23978,28 @@
         <v>0.0771</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3417448167234349</v>
+        <v>-0.3582098790857725</v>
       </c>
       <c r="J9" t="n">
+        <v>234</v>
+      </c>
+      <c r="K9" t="n">
         <v>232</v>
       </c>
-      <c r="K9" t="n">
-        <v>230</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.02842722787566954</v>
+        <v>0.03163507535224186</v>
       </c>
       <c r="M9" t="n">
-        <v>13.02392817040471</v>
+        <v>12.99371247469673</v>
       </c>
       <c r="N9" t="n">
-        <v>230.3816149985416</v>
+        <v>229.2068635052748</v>
       </c>
       <c r="O9" t="n">
-        <v>15.17832714756609</v>
+        <v>15.13957937015671</v>
       </c>
       <c r="P9" t="n">
-        <v>369.0503487840705</v>
+        <v>369.2124528095268</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -23862,28 +24056,28 @@
         <v>0.1197</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04369264170606683</v>
+        <v>-0.0607139463800443</v>
       </c>
       <c r="J10" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K10" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L10" t="n">
-        <v>0.000564550867730107</v>
+        <v>0.00110627410462083</v>
       </c>
       <c r="M10" t="n">
-        <v>11.66043663024471</v>
+        <v>11.63856545781414</v>
       </c>
       <c r="N10" t="n">
-        <v>194.251318709299</v>
+        <v>193.4341460363077</v>
       </c>
       <c r="O10" t="n">
-        <v>13.93740717311864</v>
+        <v>13.90806046996876</v>
       </c>
       <c r="P10" t="n">
-        <v>367.6273125074026</v>
+        <v>367.7951887026732</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -23940,28 +24134,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1091819473325835</v>
+        <v>-0.1242974048751406</v>
       </c>
       <c r="J11" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K11" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003397660443766992</v>
+        <v>0.004470727721376133</v>
       </c>
       <c r="M11" t="n">
-        <v>11.85932789039618</v>
+        <v>11.824029381069</v>
       </c>
       <c r="N11" t="n">
-        <v>201.2635976485302</v>
+        <v>200.2005120759135</v>
       </c>
       <c r="O11" t="n">
-        <v>14.1867402051539</v>
+        <v>14.14922302021964</v>
       </c>
       <c r="P11" t="n">
-        <v>367.6600213737871</v>
+        <v>367.8095030347966</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -24018,28 +24212,28 @@
         <v>0.0809</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.397151859174689</v>
+        <v>-0.4113109742884957</v>
       </c>
       <c r="J12" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K12" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03831236836231611</v>
+        <v>0.04165423707202087</v>
       </c>
       <c r="M12" t="n">
-        <v>12.54099088978127</v>
+        <v>12.50180915665692</v>
       </c>
       <c r="N12" t="n">
-        <v>227.5641941606353</v>
+        <v>226.2055797561569</v>
       </c>
       <c r="O12" t="n">
-        <v>15.08523099460646</v>
+        <v>15.04013230514136</v>
       </c>
       <c r="P12" t="n">
-        <v>378.5881949292142</v>
+        <v>378.7278380975103</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -24096,28 +24290,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07535560381132925</v>
+        <v>-0.08926264496004822</v>
       </c>
       <c r="J13" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K13" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00185780057376006</v>
+        <v>0.002647529994408093</v>
       </c>
       <c r="M13" t="n">
-        <v>11.31326120330403</v>
+        <v>11.2771077512593</v>
       </c>
       <c r="N13" t="n">
-        <v>177.4854646597412</v>
+        <v>176.5472699994265</v>
       </c>
       <c r="O13" t="n">
-        <v>13.32236708170666</v>
+        <v>13.28710916638478</v>
       </c>
       <c r="P13" t="n">
-        <v>385.5098132924573</v>
+        <v>385.6456287747885</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24174,28 +24368,28 @@
         <v>0.079</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.05270398336588549</v>
+        <v>-0.07018535505229763</v>
       </c>
       <c r="J14" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K14" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0009464951283728595</v>
+        <v>0.001701190978981137</v>
       </c>
       <c r="M14" t="n">
-        <v>10.81512089401274</v>
+        <v>10.79993005246767</v>
       </c>
       <c r="N14" t="n">
-        <v>170.5672332416553</v>
+        <v>170.0255582575118</v>
       </c>
       <c r="O14" t="n">
-        <v>13.06013909733182</v>
+        <v>13.03938488800418</v>
       </c>
       <c r="P14" t="n">
-        <v>384.7402541735296</v>
+        <v>384.9109754731271</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24252,28 +24446,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05145572446855062</v>
+        <v>0.02424407642970922</v>
       </c>
       <c r="J15" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K15" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0009213704887817142</v>
+        <v>0.0002059871171542493</v>
       </c>
       <c r="M15" t="n">
-        <v>10.79790036212557</v>
+        <v>10.81894506328906</v>
       </c>
       <c r="N15" t="n">
-        <v>167.0210175741392</v>
+        <v>167.8013637578753</v>
       </c>
       <c r="O15" t="n">
-        <v>12.92366115209383</v>
+        <v>12.95381657110658</v>
       </c>
       <c r="P15" t="n">
-        <v>383.83813868972</v>
+        <v>384.1038901020967</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24330,28 +24524,28 @@
         <v>0.0737</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0336314178284776</v>
+        <v>-0.06414828353020725</v>
       </c>
       <c r="J16" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K16" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0004217786351226049</v>
+        <v>0.001535517817642162</v>
       </c>
       <c r="M16" t="n">
-        <v>10.30408735428666</v>
+        <v>10.35064175116665</v>
       </c>
       <c r="N16" t="n">
-        <v>155.9412175060993</v>
+        <v>157.3843575424373</v>
       </c>
       <c r="O16" t="n">
-        <v>12.48764259202269</v>
+        <v>12.54529224619488</v>
       </c>
       <c r="P16" t="n">
-        <v>388.5526774523604</v>
+        <v>388.8507083900062</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24408,28 +24602,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.242620246804943</v>
+        <v>-0.2577085187815963</v>
       </c>
       <c r="J17" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K17" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02153132528238255</v>
+        <v>0.02458736775872139</v>
       </c>
       <c r="M17" t="n">
-        <v>10.12574656390384</v>
+        <v>10.10881151916018</v>
       </c>
       <c r="N17" t="n">
-        <v>155.6211441576811</v>
+        <v>154.9699929144968</v>
       </c>
       <c r="O17" t="n">
-        <v>12.47482040582874</v>
+        <v>12.44869442610336</v>
       </c>
       <c r="P17" t="n">
-        <v>393.5030770684082</v>
+        <v>393.6504303427685</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24486,28 +24680,28 @@
         <v>0.0731</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.137584516689429</v>
+        <v>-0.158340149992324</v>
       </c>
       <c r="J18" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K18" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L18" t="n">
-        <v>0.006149285208632338</v>
+        <v>0.008228378663116875</v>
       </c>
       <c r="M18" t="n">
-        <v>10.87547999715244</v>
+        <v>10.87524105261624</v>
       </c>
       <c r="N18" t="n">
-        <v>177.3241486493621</v>
+        <v>177.0814313348302</v>
       </c>
       <c r="O18" t="n">
-        <v>13.31631137550343</v>
+        <v>13.30719472070767</v>
       </c>
       <c r="P18" t="n">
-        <v>389.0797659400448</v>
+        <v>389.2833799387444</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24564,28 +24758,28 @@
         <v>0.0774</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2409984339158525</v>
+        <v>-0.2602896214971256</v>
       </c>
       <c r="J19" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K19" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02000986283980577</v>
+        <v>0.02355716284859066</v>
       </c>
       <c r="M19" t="n">
-        <v>10.50712363640285</v>
+        <v>10.50463807790491</v>
       </c>
       <c r="N19" t="n">
-        <v>165.4795736271326</v>
+        <v>165.1776444753389</v>
       </c>
       <c r="O19" t="n">
-        <v>12.86388641224465</v>
+        <v>12.85214552031445</v>
       </c>
       <c r="P19" t="n">
-        <v>391.0370956226404</v>
+        <v>391.2254931263527</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24642,28 +24836,28 @@
         <v>0.063</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2115034428461034</v>
+        <v>-0.2302828955526407</v>
       </c>
       <c r="J20" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K20" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01407213993516754</v>
+        <v>0.0168651389535438</v>
       </c>
       <c r="M20" t="n">
-        <v>11.0752706834997</v>
+        <v>11.07270210582516</v>
       </c>
       <c r="N20" t="n">
-        <v>182.3300434518996</v>
+        <v>181.8277901508459</v>
       </c>
       <c r="O20" t="n">
-        <v>13.50296424685704</v>
+        <v>13.48435353106873</v>
       </c>
       <c r="P20" t="n">
-        <v>391.2273308007047</v>
+        <v>391.4107296104926</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24720,28 +24914,28 @@
         <v>0.0594</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2455500440366739</v>
+        <v>-0.2596506801857164</v>
       </c>
       <c r="J21" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K21" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01851830720309344</v>
+        <v>0.02099462960465326</v>
       </c>
       <c r="M21" t="n">
-        <v>11.05051345725237</v>
+        <v>11.02505500040141</v>
       </c>
       <c r="N21" t="n">
-        <v>185.9085274265076</v>
+        <v>184.9138800072218</v>
       </c>
       <c r="O21" t="n">
-        <v>13.63482773732428</v>
+        <v>13.59830430631782</v>
       </c>
       <c r="P21" t="n">
-        <v>395.7291214134714</v>
+        <v>395.8668280712208</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24798,28 +24992,28 @@
         <v>0.0436</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.02410228623812671</v>
+        <v>-0.04431520891727497</v>
       </c>
       <c r="J22" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K22" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0001130605184064271</v>
+        <v>0.0003880462456320455</v>
       </c>
       <c r="M22" t="n">
-        <v>13.77556825276728</v>
+        <v>13.76629260515942</v>
       </c>
       <c r="N22" t="n">
-        <v>300.1245233223428</v>
+        <v>298.7787917237357</v>
       </c>
       <c r="O22" t="n">
-        <v>17.32410238143214</v>
+        <v>17.28521887983301</v>
       </c>
       <c r="P22" t="n">
-        <v>385.4558734562505</v>
+        <v>385.6529209658299</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -24876,28 +25070,28 @@
         <v>0.0402</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1251356237216234</v>
+        <v>-0.1522900196967907</v>
       </c>
       <c r="J23" t="n">
+        <v>234</v>
+      </c>
+      <c r="K23" t="n">
         <v>232</v>
       </c>
-      <c r="K23" t="n">
-        <v>230</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.002749341167740393</v>
+        <v>0.004119012304695469</v>
       </c>
       <c r="M23" t="n">
-        <v>14.93218072233936</v>
+        <v>14.9578226593019</v>
       </c>
       <c r="N23" t="n">
-        <v>330.1513205996131</v>
+        <v>329.5144274056473</v>
       </c>
       <c r="O23" t="n">
-        <v>18.17006660966363</v>
+        <v>18.15253225876895</v>
       </c>
       <c r="P23" t="n">
-        <v>383.2690982230404</v>
+        <v>383.5352504174406</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -24954,28 +25148,28 @@
         <v>0.0493</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2886265244317032</v>
+        <v>0.2522572935389469</v>
       </c>
       <c r="J24" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K24" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01811958100032873</v>
+        <v>0.01396314544446797</v>
       </c>
       <c r="M24" t="n">
-        <v>13.11010699191204</v>
+        <v>13.19232090250275</v>
       </c>
       <c r="N24" t="n">
-        <v>261.1239029322113</v>
+        <v>262.7810046817318</v>
       </c>
       <c r="O24" t="n">
-        <v>16.15932866588867</v>
+        <v>16.21052141918118</v>
       </c>
       <c r="P24" t="n">
-        <v>380.538212926735</v>
+        <v>380.8965596982401</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -25032,28 +25226,28 @@
         <v>0.0531</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3644606801533912</v>
+        <v>0.3420331267129232</v>
       </c>
       <c r="J25" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K25" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L25" t="n">
-        <v>0.03195102906483638</v>
+        <v>0.02861048372729591</v>
       </c>
       <c r="M25" t="n">
-        <v>12.39132605704159</v>
+        <v>12.38867017998512</v>
       </c>
       <c r="N25" t="n">
-        <v>232.7970863141456</v>
+        <v>232.2743062349087</v>
       </c>
       <c r="O25" t="n">
-        <v>15.25768941596812</v>
+        <v>15.24054809496393</v>
       </c>
       <c r="P25" t="n">
-        <v>382.9057401320424</v>
+        <v>383.1267173704808</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -25110,28 +25304,28 @@
         <v>0.0699</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2268334525909768</v>
+        <v>0.2224433452832271</v>
       </c>
       <c r="J26" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K26" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01416923768647826</v>
+        <v>0.01389526099227945</v>
       </c>
       <c r="M26" t="n">
-        <v>11.45801564441199</v>
+        <v>11.38172827944671</v>
       </c>
       <c r="N26" t="n">
-        <v>207.0779166874385</v>
+        <v>205.348621611451</v>
       </c>
       <c r="O26" t="n">
-        <v>14.39020210724778</v>
+        <v>14.3299902865093</v>
       </c>
       <c r="P26" t="n">
-        <v>385.2843444964375</v>
+        <v>385.3275940424823</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -25169,7 +25363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA233"/>
+  <dimension ref="A1:AA235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56981,6 +57175,280 @@
         </is>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>-34.77192417541545,173.1492291832718</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>-34.77246141582987,173.14861364720971</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>-34.773041625441586,173.14806958211418</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-34.773697227621454,173.14765249940902</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>-34.77437469458005,173.14727466614934</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-34.775102539517086,173.14707557170374</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-34.77583630443794,173.14686154980876</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-34.77658720098186,173.14690916716202</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-34.77732892508208,173.1470272675113</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-34.77806233548576,173.14716737946102</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-34.77878236628743,173.1473711055754</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>-34.77947361061011,173.14770116576668</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>-34.78015740801025,173.14799549397847</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>-34.78084667289134,173.14831428927818</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>-34.78152046501358,173.14867621614914</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>-34.78212983173892,173.14917210656827</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>-34.78277143807439,173.1496056689319</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>-34.78339369084403,173.1500883454268</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>-34.78400957110401,173.15058308194898</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>-34.78459268694466,173.15112480270116</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>-34.78521494983843,173.1515963667415</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>-34.785834514840694,173.15209227549235</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>-34.78639042058852,173.1526836133351</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>-34.78690084656279,173.15334687012142</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>-34.787429929712715,173.15398098004437</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>-34.77193243001108,173.14924147277222</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>-34.77246725259607,173.14862323173742</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>-34.77304707877422,173.14808153780578</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-34.77370325672918,173.14766874568392</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>-34.77438102935807,173.14730054547152</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-34.77510529940883,173.14709838773877</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-34.77583793196638,173.1468905538497</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-34.776586611269565,173.14693735507484</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-34.777327766445644,173.1470401971788</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-34.77805929308457,173.1471882591272</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>-34.778779133181295,173.14739238796133</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>-34.77947050987759,173.14771441416184</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>-34.78015122753219,173.14801368522774</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>-34.7808412081795,173.14832952490852</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>-34.781514304960815,173.14869190882715</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>-34.782125907610066,173.14918034054455</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>-34.78276589665396,173.14961616381555</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>-34.783386156420384,173.15010261486415</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>-34.784000918626006,173.15059946887393</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>-34.78458680593693,173.15113488917387</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>-34.78520352310125,173.15161356142298</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>-34.785818443354614,173.15211602171323</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>-34.78637931400512,173.15270055879313</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>-34.78689151522779,173.15336133647355</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>-34.78742020951844,173.15399604920523</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0018/nzd0018.xlsx
+++ b/data/nzd0018/nzd0018.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA235"/>
+  <dimension ref="A1:AA236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20867,6 +20867,93 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>376.45</v>
+      </c>
+      <c r="C236" t="n">
+        <v>370.72</v>
+      </c>
+      <c r="D236" t="n">
+        <v>367.02</v>
+      </c>
+      <c r="E236" t="n">
+        <v>361.62</v>
+      </c>
+      <c r="F236" t="n">
+        <v>359.41</v>
+      </c>
+      <c r="G236" t="n">
+        <v>355.54</v>
+      </c>
+      <c r="H236" t="n">
+        <v>346.15</v>
+      </c>
+      <c r="I236" t="n">
+        <v>352.88</v>
+      </c>
+      <c r="J236" t="n">
+        <v>358.68</v>
+      </c>
+      <c r="K236" t="n">
+        <v>359.3</v>
+      </c>
+      <c r="L236" t="n">
+        <v>363.18</v>
+      </c>
+      <c r="M236" t="n">
+        <v>377.22</v>
+      </c>
+      <c r="N236" t="n">
+        <v>379.29</v>
+      </c>
+      <c r="O236" t="n">
+        <v>374.41</v>
+      </c>
+      <c r="P236" t="n">
+        <v>374.98</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>377.89</v>
+      </c>
+      <c r="R236" t="n">
+        <v>374.91</v>
+      </c>
+      <c r="S236" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="T236" t="n">
+        <v>376.82</v>
+      </c>
+      <c r="U236" t="n">
+        <v>382.47</v>
+      </c>
+      <c r="V236" t="n">
+        <v>375.84</v>
+      </c>
+      <c r="W236" t="n">
+        <v>365.3</v>
+      </c>
+      <c r="X236" t="n">
+        <v>365.82</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>378.37</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20881,7 +20968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B238"/>
+  <dimension ref="A1:B239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23264,6 +23351,16 @@
       </c>
       <c r="B238" t="n">
         <v>0.92</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -23432,28 +23529,28 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04799666502486673</v>
+        <v>0.04216348493789752</v>
       </c>
       <c r="J2" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K2" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002186620199779665</v>
+        <v>0.0016997277651849</v>
       </c>
       <c r="M2" t="n">
-        <v>6.439035859646825</v>
+        <v>6.437320039536325</v>
       </c>
       <c r="N2" t="n">
-        <v>61.83178963277663</v>
+        <v>61.76858397776399</v>
       </c>
       <c r="O2" t="n">
-        <v>7.863319250340573</v>
+        <v>7.859299203985302</v>
       </c>
       <c r="P2" t="n">
-        <v>382.0761044319462</v>
+        <v>382.1338207765711</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23510,28 +23607,28 @@
         <v>0.1142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05562751390699439</v>
+        <v>0.05024781741365358</v>
       </c>
       <c r="J3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002650732007624779</v>
+        <v>0.002180194812238412</v>
       </c>
       <c r="M3" t="n">
-        <v>6.928115954867519</v>
+        <v>6.923394803669161</v>
       </c>
       <c r="N3" t="n">
-        <v>68.4816913655489</v>
+        <v>68.36031388517377</v>
       </c>
       <c r="O3" t="n">
-        <v>8.275366539649401</v>
+        <v>8.268029625320278</v>
       </c>
       <c r="P3" t="n">
-        <v>375.6041951123505</v>
+        <v>375.6574244678919</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23588,28 +23685,28 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09511013078141589</v>
+        <v>-0.09833146807186101</v>
       </c>
       <c r="J4" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K4" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005288079050292271</v>
+        <v>0.005703396505420177</v>
       </c>
       <c r="M4" t="n">
-        <v>8.562819745449739</v>
+        <v>8.540381879733875</v>
       </c>
       <c r="N4" t="n">
-        <v>100.0844637925589</v>
+        <v>99.71953913805427</v>
       </c>
       <c r="O4" t="n">
-        <v>10.00422229823782</v>
+        <v>9.985967110803754</v>
       </c>
       <c r="P4" t="n">
-        <v>373.3728984906168</v>
+        <v>373.4047719816519</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23666,28 +23763,28 @@
         <v>0.1014</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2184293948558713</v>
+        <v>-0.2209668358019811</v>
       </c>
       <c r="J5" t="n">
+        <v>235</v>
+      </c>
+      <c r="K5" t="n">
         <v>234</v>
       </c>
-      <c r="K5" t="n">
-        <v>233</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01869338370880058</v>
+        <v>0.01930685732814819</v>
       </c>
       <c r="M5" t="n">
-        <v>10.3024960058638</v>
+        <v>10.26979709175519</v>
       </c>
       <c r="N5" t="n">
-        <v>145.5588608008174</v>
+        <v>144.9739903521508</v>
       </c>
       <c r="O5" t="n">
-        <v>12.06477769380014</v>
+        <v>12.04051453851333</v>
       </c>
       <c r="P5" t="n">
-        <v>370.4145257431141</v>
+        <v>370.4398774196541</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23744,28 +23841,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2239486929844305</v>
+        <v>-0.2301731086397779</v>
       </c>
       <c r="J6" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K6" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01206713572407181</v>
+        <v>0.01285395736473671</v>
       </c>
       <c r="M6" t="n">
-        <v>13.00880859023509</v>
+        <v>12.98022818374015</v>
       </c>
       <c r="N6" t="n">
-        <v>238.3592349975545</v>
+        <v>237.5552353523298</v>
       </c>
       <c r="O6" t="n">
-        <v>15.43888710359508</v>
+        <v>15.4128269747094</v>
       </c>
       <c r="P6" t="n">
-        <v>372.6374821516083</v>
+        <v>372.6999060870903</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23822,28 +23919,28 @@
         <v>0.0711</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3240573156428198</v>
+        <v>-0.3263233198097004</v>
       </c>
       <c r="J7" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K7" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02670349484614665</v>
+        <v>0.02733081920325087</v>
       </c>
       <c r="M7" t="n">
-        <v>12.71445284058565</v>
+        <v>12.66969556444183</v>
       </c>
       <c r="N7" t="n">
-        <v>223.3587875004459</v>
+        <v>222.429965256368</v>
       </c>
       <c r="O7" t="n">
-        <v>14.94519278900229</v>
+        <v>14.91408613547501</v>
       </c>
       <c r="P7" t="n">
-        <v>366.842399156261</v>
+        <v>366.8650018852933</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23900,28 +23997,28 @@
         <v>0.0594</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1200809783152627</v>
+        <v>-0.1307680184262513</v>
       </c>
       <c r="J8" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K8" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002735509936497627</v>
+        <v>0.003268057911850475</v>
       </c>
       <c r="M8" t="n">
-        <v>15.00389930651963</v>
+        <v>14.9924517160973</v>
       </c>
       <c r="N8" t="n">
-        <v>306.7628871261094</v>
+        <v>306.1091311265965</v>
       </c>
       <c r="O8" t="n">
-        <v>17.51464778766931</v>
+        <v>17.4959747121044</v>
       </c>
       <c r="P8" t="n">
-        <v>361.8670121269352</v>
+        <v>361.9736122273751</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23978,28 +24075,28 @@
         <v>0.0771</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3582098790857725</v>
+        <v>-0.3639997978942919</v>
       </c>
       <c r="J9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03163507535224186</v>
+        <v>0.03292437583778896</v>
       </c>
       <c r="M9" t="n">
-        <v>12.99371247469673</v>
+        <v>12.96596405692331</v>
       </c>
       <c r="N9" t="n">
-        <v>229.2068635052748</v>
+        <v>228.4176914250471</v>
       </c>
       <c r="O9" t="n">
-        <v>15.13957937015671</v>
+        <v>15.11349368693576</v>
       </c>
       <c r="P9" t="n">
-        <v>369.2124528095268</v>
+        <v>369.2702055567905</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24056,28 +24153,28 @@
         <v>0.1197</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0607139463800443</v>
+        <v>-0.06712056656233717</v>
       </c>
       <c r="J10" t="n">
+        <v>235</v>
+      </c>
+      <c r="K10" t="n">
         <v>234</v>
       </c>
-      <c r="K10" t="n">
-        <v>233</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.00110627410462083</v>
+        <v>0.001363721452012578</v>
       </c>
       <c r="M10" t="n">
-        <v>11.63856545781414</v>
+        <v>11.61743997434108</v>
       </c>
       <c r="N10" t="n">
-        <v>193.4341460363077</v>
+        <v>192.8444934575039</v>
       </c>
       <c r="O10" t="n">
-        <v>13.90806046996876</v>
+        <v>13.886846058681</v>
       </c>
       <c r="P10" t="n">
-        <v>367.7951887026732</v>
+        <v>367.8591975076167</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24134,28 +24231,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1242974048751406</v>
+        <v>-0.1287458679601534</v>
       </c>
       <c r="J11" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K11" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004470727721376133</v>
+        <v>0.004840283286770775</v>
       </c>
       <c r="M11" t="n">
-        <v>11.824029381069</v>
+        <v>11.79276312853013</v>
       </c>
       <c r="N11" t="n">
-        <v>200.2005120759135</v>
+        <v>199.4523306938738</v>
       </c>
       <c r="O11" t="n">
-        <v>14.14922302021964</v>
+        <v>14.12275931586579</v>
       </c>
       <c r="P11" t="n">
-        <v>367.8095030347966</v>
+        <v>367.8540740707809</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -24212,28 +24309,28 @@
         <v>0.0809</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4113109742884957</v>
+        <v>-0.4152202184134096</v>
       </c>
       <c r="J12" t="n">
+        <v>235</v>
+      </c>
+      <c r="K12" t="n">
         <v>234</v>
       </c>
-      <c r="K12" t="n">
-        <v>233</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.04165423707202087</v>
+        <v>0.04281101698162848</v>
       </c>
       <c r="M12" t="n">
-        <v>12.50180915665692</v>
+        <v>12.46674853672339</v>
       </c>
       <c r="N12" t="n">
-        <v>226.2055797561569</v>
+        <v>225.3271273036653</v>
       </c>
       <c r="O12" t="n">
-        <v>15.04013230514136</v>
+        <v>15.01090028291659</v>
       </c>
       <c r="P12" t="n">
-        <v>378.7278380975103</v>
+        <v>378.7668955158602</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -24290,28 +24387,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08926264496004822</v>
+        <v>-0.09437147193049548</v>
       </c>
       <c r="J13" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K13" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002647529994408093</v>
+        <v>0.002985438465319734</v>
       </c>
       <c r="M13" t="n">
-        <v>11.2771077512593</v>
+        <v>11.25084471325399</v>
       </c>
       <c r="N13" t="n">
-        <v>176.5472699994265</v>
+        <v>175.9493475205715</v>
       </c>
       <c r="O13" t="n">
-        <v>13.28710916638478</v>
+        <v>13.26458998690014</v>
       </c>
       <c r="P13" t="n">
-        <v>385.6456287747885</v>
+        <v>385.6961780144243</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24368,28 +24465,28 @@
         <v>0.079</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.07018535505229763</v>
+        <v>-0.07335571992486244</v>
       </c>
       <c r="J14" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K14" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001701190978981137</v>
+        <v>0.001876081047271327</v>
       </c>
       <c r="M14" t="n">
-        <v>10.79993005246767</v>
+        <v>10.76763476612049</v>
       </c>
       <c r="N14" t="n">
-        <v>170.0255582575118</v>
+        <v>169.3610977922914</v>
       </c>
       <c r="O14" t="n">
-        <v>13.03938488800418</v>
+        <v>13.01388096581075</v>
       </c>
       <c r="P14" t="n">
-        <v>384.9109754731271</v>
+        <v>384.9423446180606</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24446,28 +24543,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02424407642970922</v>
+        <v>0.01550766910017861</v>
       </c>
       <c r="J15" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K15" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0002059871171542493</v>
+        <v>8.491052775949637e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>10.81894506328906</v>
+        <v>10.80808848190494</v>
       </c>
       <c r="N15" t="n">
-        <v>167.8013637578753</v>
+        <v>167.5357363575353</v>
       </c>
       <c r="O15" t="n">
-        <v>12.95381657110658</v>
+        <v>12.94355964785326</v>
       </c>
       <c r="P15" t="n">
-        <v>384.1038901020967</v>
+        <v>384.190332400928</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24524,28 +24621,28 @@
         <v>0.0737</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.06414828353020725</v>
+        <v>-0.07442431844077141</v>
       </c>
       <c r="J16" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K16" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001535517817642162</v>
+        <v>0.002078325514416002</v>
       </c>
       <c r="M16" t="n">
-        <v>10.35064175116665</v>
+        <v>10.35120764680939</v>
       </c>
       <c r="N16" t="n">
-        <v>157.3843575424373</v>
+        <v>157.3350361636527</v>
       </c>
       <c r="O16" t="n">
-        <v>12.54529224619488</v>
+        <v>12.54332635960863</v>
       </c>
       <c r="P16" t="n">
-        <v>388.8507083900062</v>
+        <v>388.9523845192243</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24602,28 +24699,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2577085187815963</v>
+        <v>-0.2652152180612844</v>
       </c>
       <c r="J17" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K17" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02458736775872139</v>
+        <v>0.0262030437972125</v>
       </c>
       <c r="M17" t="n">
-        <v>10.10881151916018</v>
+        <v>10.09973352988742</v>
       </c>
       <c r="N17" t="n">
-        <v>154.9699929144968</v>
+        <v>154.6416148851237</v>
       </c>
       <c r="O17" t="n">
-        <v>12.44869442610336</v>
+        <v>12.43549817599294</v>
       </c>
       <c r="P17" t="n">
-        <v>393.6504303427685</v>
+        <v>393.7247053070525</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24680,28 +24777,28 @@
         <v>0.0731</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.158340149992324</v>
+        <v>-0.1669493034398536</v>
       </c>
       <c r="J18" t="n">
+        <v>235</v>
+      </c>
+      <c r="K18" t="n">
         <v>234</v>
       </c>
-      <c r="K18" t="n">
-        <v>233</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.008228378663116875</v>
+        <v>0.009207848411660002</v>
       </c>
       <c r="M18" t="n">
-        <v>10.87524105261624</v>
+        <v>10.86624726721591</v>
       </c>
       <c r="N18" t="n">
-        <v>177.0814313348302</v>
+        <v>176.7583370918054</v>
       </c>
       <c r="O18" t="n">
-        <v>13.30719472070767</v>
+        <v>13.2950493452189</v>
       </c>
       <c r="P18" t="n">
-        <v>389.2833799387444</v>
+        <v>389.3689460683945</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24758,28 +24855,28 @@
         <v>0.0774</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2602896214971256</v>
+        <v>-0.2674846907252196</v>
       </c>
       <c r="J19" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K19" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02355716284859066</v>
+        <v>0.02504345891758375</v>
       </c>
       <c r="M19" t="n">
-        <v>10.50463807790491</v>
+        <v>10.49174215613645</v>
       </c>
       <c r="N19" t="n">
-        <v>165.1776444753389</v>
+        <v>164.7789124815428</v>
       </c>
       <c r="O19" t="n">
-        <v>12.85214552031445</v>
+        <v>12.83662387396089</v>
       </c>
       <c r="P19" t="n">
-        <v>391.2254931263527</v>
+        <v>391.2966846700692</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24836,28 +24933,28 @@
         <v>0.063</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2302828955526407</v>
+        <v>-0.2374222608060321</v>
       </c>
       <c r="J20" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K20" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0168651389535438</v>
+        <v>0.0180557915770071</v>
       </c>
       <c r="M20" t="n">
-        <v>11.07270210582516</v>
+        <v>11.06036462216682</v>
       </c>
       <c r="N20" t="n">
-        <v>181.8277901508459</v>
+        <v>181.3535152414427</v>
       </c>
       <c r="O20" t="n">
-        <v>13.48435353106873</v>
+        <v>13.46675592863562</v>
       </c>
       <c r="P20" t="n">
-        <v>391.4107296104926</v>
+        <v>391.4813699917639</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -24914,28 +25011,28 @@
         <v>0.0594</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2596506801857164</v>
+        <v>-0.2651163648753304</v>
       </c>
       <c r="J21" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K21" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02099462960465326</v>
+        <v>0.02206304595390829</v>
       </c>
       <c r="M21" t="n">
-        <v>11.02505500040141</v>
+        <v>11.00420440907638</v>
       </c>
       <c r="N21" t="n">
-        <v>184.9138800072218</v>
+        <v>184.3025254366413</v>
       </c>
       <c r="O21" t="n">
-        <v>13.59830430631782</v>
+        <v>13.5758066219522</v>
       </c>
       <c r="P21" t="n">
-        <v>395.8668280712208</v>
+        <v>395.9209082361485</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -24992,28 +25089,28 @@
         <v>0.0436</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.04431520891727497</v>
+        <v>-0.05160942309735603</v>
       </c>
       <c r="J22" t="n">
+        <v>235</v>
+      </c>
+      <c r="K22" t="n">
         <v>234</v>
       </c>
-      <c r="K22" t="n">
-        <v>233</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.0003880462456320455</v>
+        <v>0.0005309605809020734</v>
       </c>
       <c r="M22" t="n">
-        <v>13.76629260515942</v>
+        <v>13.74617323974553</v>
       </c>
       <c r="N22" t="n">
-        <v>298.7787917237357</v>
+        <v>297.8161346233682</v>
       </c>
       <c r="O22" t="n">
-        <v>17.28521887983301</v>
+        <v>17.25735016227486</v>
       </c>
       <c r="P22" t="n">
-        <v>385.6529209658299</v>
+        <v>385.724972091002</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -25070,28 +25167,28 @@
         <v>0.0402</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1522900196967907</v>
+        <v>-0.1643223991662899</v>
       </c>
       <c r="J23" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K23" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004119012304695469</v>
+        <v>0.004827942518764838</v>
       </c>
       <c r="M23" t="n">
-        <v>14.9578226593019</v>
+        <v>14.96016671747557</v>
       </c>
       <c r="N23" t="n">
-        <v>329.5144274056473</v>
+        <v>328.9500068393725</v>
       </c>
       <c r="O23" t="n">
-        <v>18.15253225876895</v>
+        <v>18.13697898877794</v>
       </c>
       <c r="P23" t="n">
-        <v>383.5352504174406</v>
+        <v>383.6547458909529</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -25148,28 +25245,28 @@
         <v>0.0493</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2522572935389469</v>
+        <v>0.2336465654399418</v>
       </c>
       <c r="J24" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K24" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01396314544446797</v>
+        <v>0.01203036549895531</v>
       </c>
       <c r="M24" t="n">
-        <v>13.19232090250275</v>
+        <v>13.23328022181444</v>
       </c>
       <c r="N24" t="n">
-        <v>262.7810046817318</v>
+        <v>263.6693573171505</v>
       </c>
       <c r="O24" t="n">
-        <v>16.21052141918118</v>
+        <v>16.23789879624671</v>
       </c>
       <c r="P24" t="n">
-        <v>380.8965596982401</v>
+        <v>381.0823501209</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -25226,28 +25323,28 @@
         <v>0.0531</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3420331267129232</v>
+        <v>0.3301863267177483</v>
       </c>
       <c r="J25" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K25" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02861048372729591</v>
+        <v>0.0268842833218641</v>
       </c>
       <c r="M25" t="n">
-        <v>12.38867017998512</v>
+        <v>12.38924859804509</v>
       </c>
       <c r="N25" t="n">
-        <v>232.2743062349087</v>
+        <v>232.0920562008974</v>
       </c>
       <c r="O25" t="n">
-        <v>15.24054809496393</v>
+        <v>15.23456780486067</v>
       </c>
       <c r="P25" t="n">
-        <v>383.1267173704808</v>
+        <v>383.2449836718615</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -25304,28 +25401,28 @@
         <v>0.0699</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2224433452832271</v>
+        <v>0.2208133251254501</v>
       </c>
       <c r="J26" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K26" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01389526099227945</v>
+        <v>0.01383023643979508</v>
       </c>
       <c r="M26" t="n">
-        <v>11.38172827944671</v>
+        <v>11.3409380098839</v>
       </c>
       <c r="N26" t="n">
-        <v>205.348621611451</v>
+        <v>204.4790018172355</v>
       </c>
       <c r="O26" t="n">
-        <v>14.3299902865093</v>
+        <v>14.29961544298432</v>
       </c>
       <c r="P26" t="n">
-        <v>385.3275940424823</v>
+        <v>385.3438664920311</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -25363,7 +25460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA235"/>
+  <dimension ref="A1:AA236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57449,6 +57546,143 @@
         </is>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>-34.77193613034664,173.1492469818594</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>-34.77247255387847,173.14863193695183</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>-34.77305789818265,173.14810525790259</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-34.773708324137026,173.14768240053033</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-34.774377849146305,173.14728755342264</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-34.775106123451515,173.14710520010973</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-34.77583722221799,173.1468779054708</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-34.7765863118395,173.14695166754206</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-34.777326120984824,173.14705855947904</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-34.7780554038242,173.147214950657</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>-34.778775116286695,173.14741882971126</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>-34.77946708922656,173.14772902945373</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>-34.78013234272128,173.1480692695837</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>-34.78082416689483,173.14837703600594</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>-34.781495786047856,173.14873908554318</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>-34.782128704115735,173.1491744726535</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>-34.78275977192508,173.1496277634222</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>-34.78337711510979,173.15011973818554</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>-34.78399352999133,173.1506134622004</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>-34.784581133105654,173.15114461860196</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>-34.78519158724943,173.151631522199</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>-34.78581787141554,173.1521168667743</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>-34.78638924261765,173.1526854105809</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>-34.786900957650104,173.15334669790292</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>-34.78742126485391,173.15399441312508</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0018/nzd0018.xlsx
+++ b/data/nzd0018/nzd0018.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA236"/>
+  <dimension ref="A1:AA238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20954,6 +20954,180 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>375.55</v>
+      </c>
+      <c r="C237" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="D237" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="E237" t="n">
+        <v>361.29</v>
+      </c>
+      <c r="F237" t="n">
+        <v>357.92</v>
+      </c>
+      <c r="G237" t="n">
+        <v>353.15</v>
+      </c>
+      <c r="H237" t="n">
+        <v>344.09</v>
+      </c>
+      <c r="I237" t="n">
+        <v>352.3</v>
+      </c>
+      <c r="J237" t="n">
+        <v>357.7</v>
+      </c>
+      <c r="K237" t="n">
+        <v>357.63</v>
+      </c>
+      <c r="L237" t="n">
+        <v>361.54</v>
+      </c>
+      <c r="M237" t="n">
+        <v>375.92</v>
+      </c>
+      <c r="N237" t="n">
+        <v>378.23</v>
+      </c>
+      <c r="O237" t="n">
+        <v>373.74</v>
+      </c>
+      <c r="P237" t="n">
+        <v>374.69</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>375.96</v>
+      </c>
+      <c r="R237" t="n">
+        <v>373.02</v>
+      </c>
+      <c r="S237" t="n">
+        <v>374.81</v>
+      </c>
+      <c r="T237" t="n">
+        <v>375.29</v>
+      </c>
+      <c r="U237" t="n">
+        <v>380.98</v>
+      </c>
+      <c r="V237" t="n">
+        <v>373.89</v>
+      </c>
+      <c r="W237" t="n">
+        <v>361.67</v>
+      </c>
+      <c r="X237" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>375.89</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>386.27</v>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>375.07</v>
+      </c>
+      <c r="C238" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="D238" t="n">
+        <v>366</v>
+      </c>
+      <c r="E238" t="n">
+        <v>360.8</v>
+      </c>
+      <c r="F238" t="n">
+        <v>355.43</v>
+      </c>
+      <c r="G238" t="n">
+        <v>351.41</v>
+      </c>
+      <c r="H238" t="n">
+        <v>342.31</v>
+      </c>
+      <c r="I238" t="n">
+        <v>351.24</v>
+      </c>
+      <c r="J238" t="n">
+        <v>357.51</v>
+      </c>
+      <c r="K238" t="n">
+        <v>355.97</v>
+      </c>
+      <c r="L238" t="n">
+        <v>359.35</v>
+      </c>
+      <c r="M238" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="N238" t="n">
+        <v>377.55</v>
+      </c>
+      <c r="O238" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="P238" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>375</v>
+      </c>
+      <c r="R238" t="n">
+        <v>370.47</v>
+      </c>
+      <c r="S238" t="n">
+        <v>374.08</v>
+      </c>
+      <c r="T238" t="n">
+        <v>373.39</v>
+      </c>
+      <c r="U238" t="n">
+        <v>379.3</v>
+      </c>
+      <c r="V238" t="n">
+        <v>371.08</v>
+      </c>
+      <c r="W238" t="n">
+        <v>356.13</v>
+      </c>
+      <c r="X238" t="n">
+        <v>360.84</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>372.27</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>382.89</v>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20968,7 +21142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B239"/>
+  <dimension ref="A1:B241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23361,6 +23535,26 @@
       </c>
       <c r="B239" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>
@@ -23529,28 +23723,28 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04216348493789752</v>
+        <v>0.02905023598221321</v>
       </c>
       <c r="J2" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K2" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0016997277651849</v>
+        <v>0.0008166818867791914</v>
       </c>
       <c r="M2" t="n">
-        <v>6.437320039536325</v>
+        <v>6.440800452513888</v>
       </c>
       <c r="N2" t="n">
-        <v>61.76858397776399</v>
+        <v>61.7664575469064</v>
       </c>
       <c r="O2" t="n">
-        <v>7.859299203985302</v>
+        <v>7.859163921620824</v>
       </c>
       <c r="P2" t="n">
-        <v>382.1338207765711</v>
+        <v>382.2638188586549</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23607,28 +23801,28 @@
         <v>0.1142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05024781741365358</v>
+        <v>0.03935571817219594</v>
       </c>
       <c r="J3" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K3" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002180194812238412</v>
+        <v>0.001357915410417743</v>
       </c>
       <c r="M3" t="n">
-        <v>6.923394803669161</v>
+        <v>6.91476650248904</v>
       </c>
       <c r="N3" t="n">
-        <v>68.36031388517377</v>
+        <v>68.14185385070901</v>
       </c>
       <c r="O3" t="n">
-        <v>8.268029625320278</v>
+        <v>8.254807923308029</v>
       </c>
       <c r="P3" t="n">
-        <v>375.6574244678919</v>
+        <v>375.7654042933281</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23685,28 +23879,28 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09833146807186101</v>
+        <v>-0.1058141138109661</v>
       </c>
       <c r="J4" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K4" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005703396505420177</v>
+        <v>0.006717047503313478</v>
       </c>
       <c r="M4" t="n">
-        <v>8.540381879733875</v>
+        <v>8.500419827464414</v>
       </c>
       <c r="N4" t="n">
-        <v>99.71953913805427</v>
+        <v>99.04735310529858</v>
       </c>
       <c r="O4" t="n">
-        <v>9.985967110803754</v>
+        <v>9.952253669661891</v>
       </c>
       <c r="P4" t="n">
-        <v>373.4047719816519</v>
+        <v>373.4789526892077</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23763,28 +23957,28 @@
         <v>0.1014</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2209668358019811</v>
+        <v>-0.2267858314759866</v>
       </c>
       <c r="J5" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K5" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01930685732814819</v>
+        <v>0.02069864225525064</v>
       </c>
       <c r="M5" t="n">
-        <v>10.26979709175519</v>
+        <v>10.208417762871</v>
       </c>
       <c r="N5" t="n">
-        <v>144.9739903521508</v>
+        <v>143.8462617761335</v>
       </c>
       <c r="O5" t="n">
-        <v>12.04051453851333</v>
+        <v>11.99359253001925</v>
       </c>
       <c r="P5" t="n">
-        <v>370.4398774196541</v>
+        <v>370.4981278708131</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23841,28 +24035,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2301731086397779</v>
+        <v>-0.2467138506916753</v>
       </c>
       <c r="J6" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K6" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01285395736473671</v>
+        <v>0.014977505168426</v>
       </c>
       <c r="M6" t="n">
-        <v>12.98022818374015</v>
+        <v>12.94141549466575</v>
       </c>
       <c r="N6" t="n">
-        <v>237.5552353523298</v>
+        <v>236.347667186276</v>
       </c>
       <c r="O6" t="n">
-        <v>15.4128269747094</v>
+        <v>15.37360293445476</v>
       </c>
       <c r="P6" t="n">
-        <v>372.6999060870903</v>
+        <v>372.8661230247367</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23919,28 +24113,28 @@
         <v>0.0711</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3263233198097004</v>
+        <v>-0.33610246881359</v>
       </c>
       <c r="J7" t="n">
+        <v>237</v>
+      </c>
+      <c r="K7" t="n">
         <v>235</v>
       </c>
-      <c r="K7" t="n">
-        <v>233</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02733081920325087</v>
+        <v>0.02946707754845579</v>
       </c>
       <c r="M7" t="n">
-        <v>12.66969556444183</v>
+        <v>12.60383981765341</v>
       </c>
       <c r="N7" t="n">
-        <v>222.429965256368</v>
+        <v>220.8280832558345</v>
       </c>
       <c r="O7" t="n">
-        <v>14.91408613547501</v>
+        <v>14.86028543655318</v>
       </c>
       <c r="P7" t="n">
-        <v>366.8650018852933</v>
+        <v>366.9627435959536</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23997,28 +24191,28 @@
         <v>0.0594</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1307680184262513</v>
+        <v>-0.1562311841645594</v>
       </c>
       <c r="J8" t="n">
+        <v>237</v>
+      </c>
+      <c r="K8" t="n">
         <v>235</v>
       </c>
-      <c r="K8" t="n">
-        <v>233</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.003268057911850475</v>
+        <v>0.004720510727837857</v>
       </c>
       <c r="M8" t="n">
-        <v>14.9924517160973</v>
+        <v>14.98944861656829</v>
       </c>
       <c r="N8" t="n">
-        <v>306.1091311265965</v>
+        <v>305.4423173673271</v>
       </c>
       <c r="O8" t="n">
-        <v>17.4959747121044</v>
+        <v>17.47690811806617</v>
       </c>
       <c r="P8" t="n">
-        <v>361.9736122273751</v>
+        <v>362.2280924996907</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24075,28 +24269,28 @@
         <v>0.0771</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3639997978942919</v>
+        <v>-0.3769554443425117</v>
       </c>
       <c r="J9" t="n">
+        <v>237</v>
+      </c>
+      <c r="K9" t="n">
         <v>235</v>
       </c>
-      <c r="K9" t="n">
-        <v>233</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03292437583778896</v>
+        <v>0.03582557722164015</v>
       </c>
       <c r="M9" t="n">
-        <v>12.96596405692331</v>
+        <v>12.91753893885655</v>
       </c>
       <c r="N9" t="n">
-        <v>228.4176914250471</v>
+        <v>226.9761065641778</v>
       </c>
       <c r="O9" t="n">
-        <v>15.11349368693576</v>
+        <v>15.06572622093531</v>
       </c>
       <c r="P9" t="n">
-        <v>369.2702055567905</v>
+        <v>369.3996861814675</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24153,28 +24347,28 @@
         <v>0.1197</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06712056656233717</v>
+        <v>-0.08121843871157462</v>
       </c>
       <c r="J10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001363721452012578</v>
+        <v>0.002028952756051861</v>
       </c>
       <c r="M10" t="n">
-        <v>11.61743997434108</v>
+        <v>11.58119011154537</v>
       </c>
       <c r="N10" t="n">
-        <v>192.8444934575039</v>
+        <v>191.7995243145255</v>
       </c>
       <c r="O10" t="n">
-        <v>13.886846058681</v>
+        <v>13.84917052803255</v>
       </c>
       <c r="P10" t="n">
-        <v>367.8591975076167</v>
+        <v>368.0003148739907</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24231,28 +24425,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1287458679601534</v>
+        <v>-0.1414723873245792</v>
       </c>
       <c r="J11" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K11" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004840283286770775</v>
+        <v>0.005939434546922806</v>
       </c>
       <c r="M11" t="n">
-        <v>11.79276312853013</v>
+        <v>11.74790172568904</v>
       </c>
       <c r="N11" t="n">
-        <v>199.4523306938738</v>
+        <v>198.2354970656023</v>
       </c>
       <c r="O11" t="n">
-        <v>14.12275931586579</v>
+        <v>14.07961281660836</v>
       </c>
       <c r="P11" t="n">
-        <v>367.8540740707809</v>
+        <v>367.9818404922311</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -24309,28 +24503,28 @@
         <v>0.0809</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4152202184134096</v>
+        <v>-0.4272736673374616</v>
       </c>
       <c r="J12" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K12" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04281101698162848</v>
+        <v>0.04599215671556744</v>
       </c>
       <c r="M12" t="n">
-        <v>12.46674853672339</v>
+        <v>12.41702626424888</v>
       </c>
       <c r="N12" t="n">
-        <v>225.3271273036653</v>
+        <v>223.8580268981638</v>
       </c>
       <c r="O12" t="n">
-        <v>15.01090028291659</v>
+        <v>14.96188580688156</v>
       </c>
       <c r="P12" t="n">
-        <v>378.7668955158602</v>
+        <v>378.8875645776995</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -24387,28 +24581,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09437147193049548</v>
+        <v>-0.1075398425956469</v>
       </c>
       <c r="J13" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K13" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002985438465319734</v>
+        <v>0.003937934627840645</v>
       </c>
       <c r="M13" t="n">
-        <v>11.25084471325399</v>
+        <v>11.21254726169783</v>
       </c>
       <c r="N13" t="n">
-        <v>175.9493475205715</v>
+        <v>174.9918429140061</v>
       </c>
       <c r="O13" t="n">
-        <v>13.26458998690014</v>
+        <v>13.22844824285925</v>
       </c>
       <c r="P13" t="n">
-        <v>385.6961780144243</v>
+        <v>385.8267301379004</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24465,28 +24659,28 @@
         <v>0.079</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.07335571992486244</v>
+        <v>-0.08175160361263648</v>
       </c>
       <c r="J14" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K14" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001876081047271327</v>
+        <v>0.002372122807609456</v>
       </c>
       <c r="M14" t="n">
-        <v>10.76763476612049</v>
+        <v>10.71249242463282</v>
       </c>
       <c r="N14" t="n">
-        <v>169.3610977922914</v>
+        <v>168.1454352351263</v>
       </c>
       <c r="O14" t="n">
-        <v>13.01388096581075</v>
+        <v>12.96709046915021</v>
       </c>
       <c r="P14" t="n">
-        <v>384.9423446180606</v>
+        <v>385.0255800475865</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24543,28 +24737,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01550766910017861</v>
+        <v>-0.003891238668605408</v>
       </c>
       <c r="J15" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K15" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L15" t="n">
-        <v>8.491052775949637e-05</v>
+        <v>5.415432510202933e-06</v>
       </c>
       <c r="M15" t="n">
-        <v>10.80808848190494</v>
+        <v>10.79399097366889</v>
       </c>
       <c r="N15" t="n">
-        <v>167.5357363575353</v>
+        <v>167.2635662255462</v>
       </c>
       <c r="O15" t="n">
-        <v>12.94355964785326</v>
+        <v>12.93304164632382</v>
       </c>
       <c r="P15" t="n">
-        <v>384.190332400928</v>
+        <v>384.3826518739779</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24621,28 +24815,28 @@
         <v>0.0737</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07442431844077141</v>
+        <v>-0.09478018502905627</v>
       </c>
       <c r="J16" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K16" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L16" t="n">
-        <v>0.002078325514416002</v>
+        <v>0.003405681850103592</v>
       </c>
       <c r="M16" t="n">
-        <v>10.35120764680939</v>
+        <v>10.3519247947744</v>
       </c>
       <c r="N16" t="n">
-        <v>157.3350361636527</v>
+        <v>157.2572041404426</v>
       </c>
       <c r="O16" t="n">
-        <v>12.54332635960863</v>
+        <v>12.54022344858506</v>
       </c>
       <c r="P16" t="n">
-        <v>388.9523845192243</v>
+        <v>389.1541772952551</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24699,28 +24893,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2652152180612844</v>
+        <v>-0.2836200373803202</v>
       </c>
       <c r="J17" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K17" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0262030437972125</v>
+        <v>0.03023205653690186</v>
       </c>
       <c r="M17" t="n">
-        <v>10.09973352988742</v>
+        <v>10.09749607416605</v>
       </c>
       <c r="N17" t="n">
-        <v>154.6416148851237</v>
+        <v>154.3601054523448</v>
       </c>
       <c r="O17" t="n">
-        <v>12.43549817599294</v>
+        <v>12.42417423623577</v>
       </c>
       <c r="P17" t="n">
-        <v>393.7247053070525</v>
+        <v>393.9071634122023</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24777,28 +24971,28 @@
         <v>0.0731</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1669493034398536</v>
+        <v>-0.1887514301851046</v>
       </c>
       <c r="J18" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K18" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L18" t="n">
-        <v>0.009207848411660002</v>
+        <v>0.01187338776263169</v>
       </c>
       <c r="M18" t="n">
-        <v>10.86624726721591</v>
+        <v>10.87229494440626</v>
       </c>
       <c r="N18" t="n">
-        <v>176.7583370918054</v>
+        <v>176.7015036938504</v>
       </c>
       <c r="O18" t="n">
-        <v>13.2950493452189</v>
+        <v>13.29291178387378</v>
       </c>
       <c r="P18" t="n">
-        <v>389.3689460683945</v>
+        <v>389.5860665658176</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -24855,28 +25049,28 @@
         <v>0.0774</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2674846907252196</v>
+        <v>-0.2834928550801423</v>
       </c>
       <c r="J19" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K19" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02504345891758375</v>
+        <v>0.02845348174493167</v>
       </c>
       <c r="M19" t="n">
-        <v>10.49174215613645</v>
+        <v>10.47307507916166</v>
       </c>
       <c r="N19" t="n">
-        <v>164.7789124815428</v>
+        <v>164.1623392855547</v>
       </c>
       <c r="O19" t="n">
-        <v>12.83662387396089</v>
+        <v>12.81258519134818</v>
       </c>
       <c r="P19" t="n">
-        <v>391.2966846700692</v>
+        <v>391.4553824718793</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -24933,28 +25127,28 @@
         <v>0.063</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2374222608060321</v>
+        <v>-0.2552313482490878</v>
       </c>
       <c r="J20" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K20" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0180557915770071</v>
+        <v>0.02110084484507002</v>
       </c>
       <c r="M20" t="n">
-        <v>11.06036462216682</v>
+        <v>11.05312971204744</v>
       </c>
       <c r="N20" t="n">
-        <v>181.3535152414427</v>
+        <v>180.7870226940459</v>
       </c>
       <c r="O20" t="n">
-        <v>13.46675592863562</v>
+        <v>13.44570647805633</v>
       </c>
       <c r="P20" t="n">
-        <v>391.4813699917639</v>
+        <v>391.6579299732069</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -25011,28 +25205,28 @@
         <v>0.0594</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2651163648753304</v>
+        <v>-0.2794690842618085</v>
       </c>
       <c r="J21" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K21" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02206304595390829</v>
+        <v>0.02484639168191016</v>
       </c>
       <c r="M21" t="n">
-        <v>11.00420440907638</v>
+        <v>10.9789379874765</v>
       </c>
       <c r="N21" t="n">
-        <v>184.3025254366413</v>
+        <v>183.3742549967324</v>
       </c>
       <c r="O21" t="n">
-        <v>13.5758066219522</v>
+        <v>13.54157505597973</v>
       </c>
       <c r="P21" t="n">
-        <v>395.9209082361485</v>
+        <v>396.0632027922128</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -25089,28 +25283,28 @@
         <v>0.0436</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.05160942309735603</v>
+        <v>-0.07116631486230268</v>
       </c>
       <c r="J22" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K22" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0005309605809020734</v>
+        <v>0.001025021565905226</v>
       </c>
       <c r="M22" t="n">
-        <v>13.74617323974553</v>
+        <v>13.73219716103862</v>
       </c>
       <c r="N22" t="n">
-        <v>297.8161346233682</v>
+        <v>296.4679463167121</v>
       </c>
       <c r="O22" t="n">
-        <v>17.25735016227486</v>
+        <v>17.21824457709647</v>
       </c>
       <c r="P22" t="n">
-        <v>385.724972091002</v>
+        <v>385.9185421618279</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -25167,28 +25361,28 @@
         <v>0.0402</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1643223991662899</v>
+        <v>-0.1980688596986628</v>
       </c>
       <c r="J23" t="n">
+        <v>237</v>
+      </c>
+      <c r="K23" t="n">
         <v>235</v>
       </c>
-      <c r="K23" t="n">
-        <v>233</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.004827942518764838</v>
+        <v>0.007061929247799581</v>
       </c>
       <c r="M23" t="n">
-        <v>14.96016671747557</v>
+        <v>15.01862621551671</v>
       </c>
       <c r="N23" t="n">
-        <v>328.9500068393725</v>
+        <v>329.6457909734761</v>
       </c>
       <c r="O23" t="n">
-        <v>18.13697898877794</v>
+        <v>18.15615022446874</v>
       </c>
       <c r="P23" t="n">
-        <v>383.6547458909529</v>
+        <v>383.9905685010889</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -25245,28 +25439,28 @@
         <v>0.0493</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2336465654399418</v>
+        <v>0.1926009630042076</v>
       </c>
       <c r="J24" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K24" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01203036549895531</v>
+        <v>0.008209923221482174</v>
       </c>
       <c r="M24" t="n">
-        <v>13.23328022181444</v>
+        <v>13.33443522359427</v>
       </c>
       <c r="N24" t="n">
-        <v>263.6693573171505</v>
+        <v>266.4907581014929</v>
       </c>
       <c r="O24" t="n">
-        <v>16.23789879624671</v>
+        <v>16.32454465219453</v>
       </c>
       <c r="P24" t="n">
-        <v>381.0823501209</v>
+        <v>381.4929142648166</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -25323,28 +25517,28 @@
         <v>0.0531</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3301863267177483</v>
+        <v>0.3002224551901853</v>
       </c>
       <c r="J25" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K25" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0268842833218641</v>
+        <v>0.02250378563128186</v>
       </c>
       <c r="M25" t="n">
-        <v>12.38924859804509</v>
+        <v>12.42227709600019</v>
       </c>
       <c r="N25" t="n">
-        <v>232.0920562008974</v>
+        <v>232.8254372437416</v>
       </c>
       <c r="O25" t="n">
-        <v>15.23456780486067</v>
+        <v>15.25861845789918</v>
       </c>
       <c r="P25" t="n">
-        <v>383.2449836718615</v>
+        <v>383.5447089375577</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -25401,28 +25595,28 @@
         <v>0.0699</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2208133251254501</v>
+        <v>0.2097093703142575</v>
       </c>
       <c r="J26" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K26" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01383023643979508</v>
+        <v>0.01271163179589752</v>
       </c>
       <c r="M26" t="n">
-        <v>11.3409380098839</v>
+        <v>11.29977983433866</v>
       </c>
       <c r="N26" t="n">
-        <v>204.4790018172355</v>
+        <v>203.1248084942044</v>
       </c>
       <c r="O26" t="n">
-        <v>14.29961544298432</v>
+        <v>14.25218609526989</v>
       </c>
       <c r="P26" t="n">
-        <v>385.3438664920311</v>
+        <v>385.4549545480286</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -25460,7 +25654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA236"/>
+  <dimension ref="A1:AA238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57683,6 +57877,280 @@
         </is>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>-34.771931006805026,173.14923935389268</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>-34.77247228613696,173.14863149729453</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>-34.77305554234411,173.14810009304227</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-34.77370710352067,173.14767911140657</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-34.77437402776099,173.1472719420104</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-34.77510299731933,173.147079356354</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-34.775835961799494,173.14685544369505</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-34.776586444411805,173.14694533072452</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>-34.777327075157714,173.14704791151803</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>-34.7780580228026,173.1471969769255</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>-34.77877779421708,173.14740120187824</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>-34.77947028839664,173.14771536047573</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>-34.780135982341356,173.14805855696434</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>-34.780826575685126,173.14837032030346</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>-34.78149690958076,173.14873622335807</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>-34.78213740936548,173.14915620647395</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>-34.78276895901799,173.1496103640116</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>-34.783381781592986,173.15011090034272</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>-34.784000967235436,173.15059937681258</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>-34.78458888770968,173.15113131874122</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>-34.78520261801306,173.15161492337774</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>-34.78583863280078,173.15208619104993</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>-34.78639647872391,173.1526743703561</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>-34.786914732474784,173.15332534280566</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>-34.78743837239422,173.1539678913989</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>-34.771928274249284,173.14923528564412</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>-34.772469394528414,173.14862674899564</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>-34.77305344826523,173.14809550205555</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-34.77370529109018,173.14767422755637</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-34.77436764168307,173.14724585314343</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-34.77510072138701,173.14706054123596</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-34.77583487269668,173.1468360349767</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-34.77658668669825,173.14693374964418</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>-34.77732726015031,173.14704584711743</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>-34.778060626095844,173.14717911082005</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>-34.77878137022988,173.1473776622702</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>-34.77947385669992,173.1477001143067</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>-34.780138317191465,173.14805168471747</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>-34.780833047060256,173.14835227811582</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>-34.78149741323342,173.14873494030957</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>-34.78214173943686,173.14914712070444</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>-34.78278135429814,173.14958688861026</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>-34.78338533006414,173.15010417989907</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>-34.78401020302646,173.15058188515096</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>-34.78459763115407,173.15111632292206</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>-34.7852185136223,173.15159100404287</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>-34.78587031820574,173.15203937462553</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>-34.786417177347886,173.15264279016756</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>-34.78693483926856,173.15329417123965</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>-34.78745714624672,173.1539387863751</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0018/nzd0018.xlsx
+++ b/data/nzd0018/nzd0018.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA238"/>
+  <dimension ref="A1:AA239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21128,6 +21128,93 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="C239" t="n">
+        <v>368.42</v>
+      </c>
+      <c r="D239" t="n">
+        <v>363.23</v>
+      </c>
+      <c r="E239" t="n">
+        <v>358.69</v>
+      </c>
+      <c r="F239" t="n">
+        <v>354.54</v>
+      </c>
+      <c r="G239" t="n">
+        <v>348.11</v>
+      </c>
+      <c r="H239" t="n">
+        <v>341.31</v>
+      </c>
+      <c r="I239" t="n">
+        <v>350.32</v>
+      </c>
+      <c r="J239" t="n">
+        <v>355.11</v>
+      </c>
+      <c r="K239" t="n">
+        <v>351.96</v>
+      </c>
+      <c r="L239" t="n">
+        <v>356.69</v>
+      </c>
+      <c r="M239" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="N239" t="n">
+        <v>375.71</v>
+      </c>
+      <c r="O239" t="n">
+        <v>369.78</v>
+      </c>
+      <c r="P239" t="n">
+        <v>372.73</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="R239" t="n">
+        <v>365.99</v>
+      </c>
+      <c r="S239" t="n">
+        <v>370.26</v>
+      </c>
+      <c r="T239" t="n">
+        <v>370.74</v>
+      </c>
+      <c r="U239" t="n">
+        <v>375.08</v>
+      </c>
+      <c r="V239" t="n">
+        <v>367.06</v>
+      </c>
+      <c r="W239" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="X239" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>369.53</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>378</v>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21142,7 +21229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B241"/>
+  <dimension ref="A1:B242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23555,6 +23642,16 @@
       </c>
       <c r="B241" t="n">
         <v>-0.36</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -23723,28 +23820,28 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02905023598221321</v>
+        <v>0.02036309107515588</v>
       </c>
       <c r="J2" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K2" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008166818867791914</v>
+        <v>0.0004023057101339989</v>
       </c>
       <c r="M2" t="n">
-        <v>6.440800452513888</v>
+        <v>6.45188163752018</v>
       </c>
       <c r="N2" t="n">
-        <v>61.7664575469064</v>
+        <v>61.97274554477676</v>
       </c>
       <c r="O2" t="n">
-        <v>7.859163921620824</v>
+        <v>7.872277024138363</v>
       </c>
       <c r="P2" t="n">
-        <v>382.2638188586549</v>
+        <v>382.3502668657145</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23801,28 +23898,28 @@
         <v>0.1142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03935571817219594</v>
+        <v>0.03247559880460614</v>
       </c>
       <c r="J3" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K3" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001357915410417743</v>
+        <v>0.0009300433143279996</v>
       </c>
       <c r="M3" t="n">
-        <v>6.91476650248904</v>
+        <v>6.917335840587143</v>
       </c>
       <c r="N3" t="n">
-        <v>68.14185385070901</v>
+        <v>68.14772152441955</v>
       </c>
       <c r="O3" t="n">
-        <v>8.254807923308029</v>
+        <v>8.255163325120803</v>
       </c>
       <c r="P3" t="n">
-        <v>375.7654042933281</v>
+        <v>375.8338701257764</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23879,28 +23976,28 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1058141138109661</v>
+        <v>-0.1118885652302681</v>
       </c>
       <c r="J4" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K4" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006717047503313478</v>
+        <v>0.007559692308496513</v>
       </c>
       <c r="M4" t="n">
-        <v>8.500419827464414</v>
+        <v>8.490445540474884</v>
       </c>
       <c r="N4" t="n">
-        <v>99.04735310529858</v>
+        <v>98.85894367287429</v>
       </c>
       <c r="O4" t="n">
-        <v>9.952253669661891</v>
+        <v>9.942783497234277</v>
       </c>
       <c r="P4" t="n">
-        <v>373.4789526892077</v>
+        <v>373.5394011132638</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23957,28 +24054,28 @@
         <v>0.1014</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2267858314759866</v>
+        <v>-0.2315335277720221</v>
       </c>
       <c r="J5" t="n">
+        <v>238</v>
+      </c>
+      <c r="K5" t="n">
         <v>237</v>
       </c>
-      <c r="K5" t="n">
-        <v>236</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.02069864225525064</v>
+        <v>0.02174174594207201</v>
       </c>
       <c r="M5" t="n">
-        <v>10.208417762871</v>
+        <v>10.18601841213669</v>
       </c>
       <c r="N5" t="n">
-        <v>143.8462617761335</v>
+        <v>143.3760816010754</v>
       </c>
       <c r="O5" t="n">
-        <v>11.99359253001925</v>
+        <v>11.97397517957489</v>
       </c>
       <c r="P5" t="n">
-        <v>370.4981278708131</v>
+        <v>370.5458315257338</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24035,28 +24132,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2467138506916753</v>
+        <v>-0.2564626388247961</v>
       </c>
       <c r="J6" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K6" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L6" t="n">
-        <v>0.014977505168426</v>
+        <v>0.01628162780557019</v>
       </c>
       <c r="M6" t="n">
-        <v>12.94141549466575</v>
+        <v>12.92834676849099</v>
       </c>
       <c r="N6" t="n">
-        <v>236.347667186276</v>
+        <v>235.9178398140581</v>
       </c>
       <c r="O6" t="n">
-        <v>15.37360293445476</v>
+        <v>15.35961717667657</v>
       </c>
       <c r="P6" t="n">
-        <v>372.8661230247367</v>
+        <v>372.9644500088826</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24113,28 +24210,28 @@
         <v>0.0711</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.33610246881359</v>
+        <v>-0.3442493237279421</v>
       </c>
       <c r="J7" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K7" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02946707754845579</v>
+        <v>0.03110547059815538</v>
       </c>
       <c r="M7" t="n">
-        <v>12.60383981765341</v>
+        <v>12.58590211145936</v>
       </c>
       <c r="N7" t="n">
-        <v>220.8280832558345</v>
+        <v>220.2971289996927</v>
       </c>
       <c r="O7" t="n">
-        <v>14.86028543655318</v>
+        <v>14.84240981106817</v>
       </c>
       <c r="P7" t="n">
-        <v>366.9627435959536</v>
+        <v>367.0444705342853</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24191,28 +24288,28 @@
         <v>0.0594</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1562311841645594</v>
+        <v>-0.1700808473765299</v>
       </c>
       <c r="J8" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K8" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004720510727837857</v>
+        <v>0.005622543879796216</v>
       </c>
       <c r="M8" t="n">
-        <v>14.98944861656829</v>
+        <v>14.99290102132915</v>
       </c>
       <c r="N8" t="n">
-        <v>305.4423173673271</v>
+        <v>305.3178224324095</v>
       </c>
       <c r="O8" t="n">
-        <v>17.47690811806617</v>
+        <v>17.47334605713541</v>
       </c>
       <c r="P8" t="n">
-        <v>362.2280924996907</v>
+        <v>362.3670283937428</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24269,28 +24366,28 @@
         <v>0.0771</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3769554443425117</v>
+        <v>-0.3843808155765345</v>
       </c>
       <c r="J9" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K9" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03582557722164015</v>
+        <v>0.03749452971596556</v>
       </c>
       <c r="M9" t="n">
-        <v>12.91753893885655</v>
+        <v>12.89788150438834</v>
       </c>
       <c r="N9" t="n">
-        <v>226.9761065641778</v>
+        <v>226.3505852594739</v>
       </c>
       <c r="O9" t="n">
-        <v>15.06572622093531</v>
+        <v>15.04495215211647</v>
       </c>
       <c r="P9" t="n">
-        <v>369.3996861814675</v>
+        <v>369.4741754001062</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24347,28 +24444,28 @@
         <v>0.1197</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08121843871157462</v>
+        <v>-0.09009260742130484</v>
       </c>
       <c r="J10" t="n">
+        <v>238</v>
+      </c>
+      <c r="K10" t="n">
         <v>237</v>
       </c>
-      <c r="K10" t="n">
-        <v>236</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.002028952756051861</v>
+        <v>0.002513499540576558</v>
       </c>
       <c r="M10" t="n">
-        <v>11.58119011154537</v>
+        <v>11.57113896548105</v>
       </c>
       <c r="N10" t="n">
-        <v>191.7995243145255</v>
+        <v>191.4680675473289</v>
       </c>
       <c r="O10" t="n">
-        <v>13.84917052803255</v>
+        <v>13.83719868858321</v>
       </c>
       <c r="P10" t="n">
-        <v>368.0003148739907</v>
+        <v>368.0894802829474</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24425,28 +24522,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1414723873245792</v>
+        <v>-0.1516200320081055</v>
       </c>
       <c r="J11" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K11" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005939434546922806</v>
+        <v>0.006860490041912803</v>
       </c>
       <c r="M11" t="n">
-        <v>11.74790172568904</v>
+        <v>11.74316662181405</v>
       </c>
       <c r="N11" t="n">
-        <v>198.2354970656023</v>
+        <v>198.0193207017073</v>
       </c>
       <c r="O11" t="n">
-        <v>14.07961281660836</v>
+        <v>14.07193379396404</v>
       </c>
       <c r="P11" t="n">
-        <v>367.9818404922311</v>
+        <v>368.0840962022449</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -24503,28 +24600,28 @@
         <v>0.0809</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4272736673374616</v>
+        <v>-0.4361697887848753</v>
       </c>
       <c r="J12" t="n">
+        <v>238</v>
+      </c>
+      <c r="K12" t="n">
         <v>237</v>
       </c>
-      <c r="K12" t="n">
-        <v>236</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.04599215671556744</v>
+        <v>0.04818191718144427</v>
       </c>
       <c r="M12" t="n">
-        <v>12.41702626424888</v>
+        <v>12.40566465801098</v>
       </c>
       <c r="N12" t="n">
-        <v>223.8580268981638</v>
+        <v>223.3936691738399</v>
       </c>
       <c r="O12" t="n">
-        <v>14.96188580688156</v>
+        <v>14.94635972984191</v>
       </c>
       <c r="P12" t="n">
-        <v>378.8875645776995</v>
+        <v>378.9769505622275</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -24581,28 +24678,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1075398425956469</v>
+        <v>-0.1167631599294266</v>
       </c>
       <c r="J13" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K13" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003937934627840645</v>
+        <v>0.004670110166944186</v>
       </c>
       <c r="M13" t="n">
-        <v>11.21254726169783</v>
+        <v>11.20460772543619</v>
       </c>
       <c r="N13" t="n">
-        <v>174.9918429140061</v>
+        <v>174.7816683502384</v>
       </c>
       <c r="O13" t="n">
-        <v>13.22844824285925</v>
+        <v>13.2205018191534</v>
       </c>
       <c r="P13" t="n">
-        <v>385.8267301379004</v>
+        <v>385.9185137342964</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -24659,28 +24756,28 @@
         <v>0.079</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.08175160361263648</v>
+        <v>-0.08758575935759169</v>
       </c>
       <c r="J14" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K14" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002372122807609456</v>
+        <v>0.002744836725794508</v>
       </c>
       <c r="M14" t="n">
-        <v>10.71249242463282</v>
+        <v>10.69199969390825</v>
       </c>
       <c r="N14" t="n">
-        <v>168.1454352351263</v>
+        <v>167.6490348080667</v>
       </c>
       <c r="O14" t="n">
-        <v>12.96709046915021</v>
+        <v>12.94793554231974</v>
       </c>
       <c r="P14" t="n">
-        <v>385.0255800475865</v>
+        <v>385.0836372277559</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -24737,28 +24834,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.003891238668605408</v>
+        <v>-0.01577301629475496</v>
       </c>
       <c r="J15" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K15" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L15" t="n">
-        <v>5.415432510202933e-06</v>
+        <v>8.937088081406586e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>10.79399097366889</v>
+        <v>10.79569386849626</v>
       </c>
       <c r="N15" t="n">
-        <v>167.2635662255462</v>
+        <v>167.432179790298</v>
       </c>
       <c r="O15" t="n">
-        <v>12.93304164632382</v>
+        <v>12.93955871698483</v>
       </c>
       <c r="P15" t="n">
-        <v>384.3826518739779</v>
+        <v>384.5008904905885</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -24815,28 +24912,28 @@
         <v>0.0737</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.09478018502905627</v>
+        <v>-0.1061566057654784</v>
       </c>
       <c r="J16" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K16" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003405681850103592</v>
+        <v>0.004288250690542617</v>
       </c>
       <c r="M16" t="n">
-        <v>10.3519247947744</v>
+        <v>10.35750264765997</v>
       </c>
       <c r="N16" t="n">
-        <v>157.2572041404426</v>
+        <v>157.395312515252</v>
       </c>
       <c r="O16" t="n">
-        <v>12.54022344858506</v>
+        <v>12.54572885548114</v>
       </c>
       <c r="P16" t="n">
-        <v>389.1541772952551</v>
+        <v>389.2673869758414</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -24893,28 +24990,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2836200373803202</v>
+        <v>-0.2955907835252982</v>
       </c>
       <c r="J17" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K17" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03023205653690186</v>
+        <v>0.03287826222751256</v>
       </c>
       <c r="M17" t="n">
-        <v>10.09749607416605</v>
+        <v>10.1093550990111</v>
       </c>
       <c r="N17" t="n">
-        <v>154.3601054523448</v>
+        <v>154.5960338798377</v>
       </c>
       <c r="O17" t="n">
-        <v>12.42417423623577</v>
+        <v>12.4336653437286</v>
       </c>
       <c r="P17" t="n">
-        <v>393.9071634122023</v>
+        <v>394.0262873773625</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -24971,28 +25068,28 @@
         <v>0.0731</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1887514301851046</v>
+        <v>-0.2039977241584622</v>
       </c>
       <c r="J18" t="n">
+        <v>238</v>
+      </c>
+      <c r="K18" t="n">
         <v>237</v>
       </c>
-      <c r="K18" t="n">
-        <v>236</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.01187338776263169</v>
+        <v>0.01386340733684355</v>
       </c>
       <c r="M18" t="n">
-        <v>10.87229494440626</v>
+        <v>10.89528599236451</v>
       </c>
       <c r="N18" t="n">
-        <v>176.7015036938504</v>
+        <v>177.3847938028188</v>
       </c>
       <c r="O18" t="n">
-        <v>13.29291178387378</v>
+        <v>13.31858828115123</v>
       </c>
       <c r="P18" t="n">
-        <v>389.5860665658176</v>
+        <v>389.7384678995513</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -25049,28 +25146,28 @@
         <v>0.0774</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2834928550801423</v>
+        <v>-0.2946319411647096</v>
       </c>
       <c r="J19" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K19" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02845348174493167</v>
+        <v>0.03081318504662822</v>
       </c>
       <c r="M19" t="n">
-        <v>10.47307507916166</v>
+        <v>10.47708272281574</v>
       </c>
       <c r="N19" t="n">
-        <v>164.1623392855547</v>
+        <v>164.2384508597025</v>
       </c>
       <c r="O19" t="n">
-        <v>12.81258519134818</v>
+        <v>12.81555503517903</v>
       </c>
       <c r="P19" t="n">
-        <v>391.4553824718793</v>
+        <v>391.5662303744732</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -25127,28 +25224,28 @@
         <v>0.063</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2552313482490878</v>
+        <v>-0.266762524488658</v>
       </c>
       <c r="J20" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K20" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02110084484507002</v>
+        <v>0.02312172875095297</v>
       </c>
       <c r="M20" t="n">
-        <v>11.05312971204744</v>
+        <v>11.06219441482314</v>
       </c>
       <c r="N20" t="n">
-        <v>180.7870226940459</v>
+        <v>180.8481479909472</v>
       </c>
       <c r="O20" t="n">
-        <v>13.44570647805633</v>
+        <v>13.44797932742861</v>
       </c>
       <c r="P20" t="n">
-        <v>391.6579299732069</v>
+        <v>391.7726796654969</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -25205,28 +25302,28 @@
         <v>0.0594</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2794690842618085</v>
+        <v>-0.2905254392972046</v>
       </c>
       <c r="J21" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K21" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02484639168191016</v>
+        <v>0.02694326236415401</v>
       </c>
       <c r="M21" t="n">
-        <v>10.9789379874765</v>
+        <v>10.98452123258109</v>
       </c>
       <c r="N21" t="n">
-        <v>183.3742549967324</v>
+        <v>183.3583101147021</v>
       </c>
       <c r="O21" t="n">
-        <v>13.54157505597973</v>
+        <v>13.54098630509248</v>
       </c>
       <c r="P21" t="n">
-        <v>396.0632027922128</v>
+        <v>396.1732274169174</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -25283,28 +25380,28 @@
         <v>0.0436</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.07116631486230268</v>
+        <v>-0.08504748935581664</v>
       </c>
       <c r="J22" t="n">
+        <v>238</v>
+      </c>
+      <c r="K22" t="n">
         <v>237</v>
       </c>
-      <c r="K22" t="n">
-        <v>236</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.001025021565905226</v>
+        <v>0.001471517286863566</v>
       </c>
       <c r="M22" t="n">
-        <v>13.73219716103862</v>
+        <v>13.74619585592259</v>
       </c>
       <c r="N22" t="n">
-        <v>296.4679463167121</v>
+        <v>296.4123759078499</v>
       </c>
       <c r="O22" t="n">
-        <v>17.21824457709647</v>
+        <v>17.21663079431774</v>
       </c>
       <c r="P22" t="n">
-        <v>385.9185421618279</v>
+        <v>386.0564503981444</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -25361,28 +25458,28 @@
         <v>0.0402</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1980688596986628</v>
+        <v>-0.2215873664393778</v>
       </c>
       <c r="J23" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K23" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L23" t="n">
-        <v>0.007061929247799581</v>
+        <v>0.008817271289507933</v>
       </c>
       <c r="M23" t="n">
-        <v>15.01862621551671</v>
+        <v>15.08385898291249</v>
       </c>
       <c r="N23" t="n">
-        <v>329.6457909734761</v>
+        <v>331.6598893220943</v>
       </c>
       <c r="O23" t="n">
-        <v>18.15615022446874</v>
+        <v>18.21153176759424</v>
       </c>
       <c r="P23" t="n">
-        <v>383.9905685010889</v>
+        <v>384.225481109034</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -25439,28 +25536,28 @@
         <v>0.0493</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1926009630042076</v>
+        <v>0.1702007859052221</v>
       </c>
       <c r="J24" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K24" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L24" t="n">
-        <v>0.008209923221482174</v>
+        <v>0.006411241666006151</v>
       </c>
       <c r="M24" t="n">
-        <v>13.33443522359427</v>
+        <v>13.39806057719913</v>
       </c>
       <c r="N24" t="n">
-        <v>266.4907581014929</v>
+        <v>268.4327941735403</v>
       </c>
       <c r="O24" t="n">
-        <v>16.32454465219453</v>
+        <v>16.38391876730168</v>
       </c>
       <c r="P24" t="n">
-        <v>381.4929142648166</v>
+        <v>381.717821439375</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -25517,28 +25614,28 @@
         <v>0.0531</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3002224551901853</v>
+        <v>0.2819656147920953</v>
       </c>
       <c r="J25" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K25" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02250378563128186</v>
+        <v>0.01992103380882826</v>
       </c>
       <c r="M25" t="n">
-        <v>12.42227709600019</v>
+        <v>12.46107835673496</v>
       </c>
       <c r="N25" t="n">
-        <v>232.8254372437416</v>
+        <v>233.8780287111146</v>
       </c>
       <c r="O25" t="n">
-        <v>15.25861845789918</v>
+        <v>15.29307126482822</v>
       </c>
       <c r="P25" t="n">
-        <v>383.5447089375577</v>
+        <v>383.7280152735815</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -25595,28 +25692,28 @@
         <v>0.0699</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2097093703142575</v>
+        <v>0.1988900985109812</v>
       </c>
       <c r="J26" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K26" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01271163179589752</v>
+        <v>0.01151844213720632</v>
       </c>
       <c r="M26" t="n">
-        <v>11.29977983433866</v>
+        <v>11.30577915030915</v>
       </c>
       <c r="N26" t="n">
-        <v>203.1248084942044</v>
+        <v>202.9780519167281</v>
       </c>
       <c r="O26" t="n">
-        <v>14.25218609526989</v>
+        <v>14.24703660122792</v>
       </c>
       <c r="P26" t="n">
-        <v>385.4549545480286</v>
+        <v>385.5635845754298</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -25654,7 +25751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA238"/>
+  <dimension ref="A1:AA239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58151,6 +58248,143 @@
         </is>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>-34.77191330211858,173.14921299503715</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>-34.77246023776688,173.14861171271806</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-34.77304136368159,173.148069008241</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-34.77369748654024,173.14765319710176</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-34.774365359107655,173.14723652820803</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-34.77509640495564,173.14702485739426</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-34.7758342608398,173.14682513120258</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-34.77658689698371,173.1469236981404</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>-34.77732959689587,173.14701977047704</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>-34.7780669147633,173.1471359523317</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>-34.77878571369137,173.14734907078008</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>-34.779480697993314,173.14767088371687</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>-34.78014463501926,173.148033089224</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>-34.780840812706856,173.14833062748696</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>-34.78150450311168,173.14871687893262</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>-34.78215666915695,173.14911579372108</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>-34.78280313109307,173.1495456455351</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>-34.78340389877015,173.15006901263655</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>-34.784023084520314,173.15055748887957</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>-34.78461959384548,173.1510786548386</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>-34.78524125395186,173.15155678490729</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>-34.78590474889605,173.15198850186383</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>-34.78642424516883,173.15263200668494</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>-34.78695005821764,173.15327057728183</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>-34.78748430722215,173.15389667878776</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
